--- a/backend/data/map_v4.6.xlsx
+++ b/backend/data/map_v4.6.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fahmy\PycharmProjects\syncDashboard\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D095759-B6F8-4ECC-B1EE-59496546D591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA85542-9876-48E8-90B8-04F39DEAEEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{58F0FD76-519D-46BD-9AA4-233998471043}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58F0FD76-519D-46BD-9AA4-233998471043}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$437</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3502" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3503" uniqueCount="874">
   <si>
     <t>local_node_region</t>
   </si>
@@ -2354,9 +2354,6 @@
     <t>upper_sync_source_port_available</t>
   </si>
   <si>
-    <t>local_node_radia_sites_count</t>
-  </si>
-  <si>
     <t>direct_parent</t>
   </si>
   <si>
@@ -2658,6 +2655,12 @@
   </si>
   <si>
     <t>Z53015_DWDM</t>
+  </si>
+  <si>
+    <t>local_node_radio_sites_count</t>
+  </si>
+  <si>
+    <t>sync_media_ready</t>
   </si>
 </sst>
 </file>
@@ -3080,26 +3083,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F7AB2-2F55-43AE-8970-69B0FC61725F}">
-  <dimension ref="A1:N437"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O437"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.88671875" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.85546875" customWidth="1"/>
     <col min="13" max="13" width="37" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="37" customWidth="1"/>
+    <col min="15" max="15" width="31.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3116,7 +3120,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>771</v>
+        <v>872</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>760</v>
@@ -3134,16 +3138,19 @@
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>770</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>762</v>
       </c>
@@ -3188,11 +3195,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N2" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>762</v>
       </c>
@@ -3237,11 +3248,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N3" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>762</v>
       </c>
@@ -3286,11 +3301,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N4" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>762</v>
       </c>
@@ -3335,11 +3354,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N5" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>762</v>
       </c>
@@ -3384,11 +3407,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N6" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>762</v>
       </c>
@@ -3433,11 +3460,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N7" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>762</v>
       </c>
@@ -3482,11 +3513,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N8" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>762</v>
       </c>
@@ -3531,11 +3566,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N9" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>762</v>
       </c>
@@ -3580,11 +3619,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N10" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>763</v>
       </c>
@@ -3629,11 +3672,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N11" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N11" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>763</v>
       </c>
@@ -3678,11 +3725,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N12" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>763</v>
       </c>
@@ -3727,11 +3778,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N13" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N13" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>763</v>
       </c>
@@ -3776,11 +3831,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N14" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N14" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>763</v>
       </c>
@@ -3825,11 +3884,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N15" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N15" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>764</v>
       </c>
@@ -3874,11 +3937,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N16" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N16" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>764</v>
       </c>
@@ -3923,11 +3990,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N17" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N17" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>764</v>
       </c>
@@ -3972,11 +4043,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N18" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N18" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>764</v>
       </c>
@@ -4021,11 +4096,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N19" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N19" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>765</v>
       </c>
@@ -4070,11 +4149,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N20" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N20" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>765</v>
       </c>
@@ -4119,11 +4202,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N21" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N21" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>765</v>
       </c>
@@ -4168,11 +4255,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N22" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N22" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>766</v>
       </c>
@@ -4217,11 +4308,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N23" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N23" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>766</v>
       </c>
@@ -4266,11 +4361,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N24" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N24" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>766</v>
       </c>
@@ -4315,11 +4414,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N25" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N25" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>766</v>
       </c>
@@ -4364,11 +4467,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N26" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N26" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>766</v>
       </c>
@@ -4413,11 +4520,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N27" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>767</v>
       </c>
@@ -4462,11 +4573,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N28" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N28" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>767</v>
       </c>
@@ -4511,11 +4626,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N29" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N29" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>767</v>
       </c>
@@ -4560,11 +4679,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N30" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>767</v>
       </c>
@@ -4609,11 +4732,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N31" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>767</v>
       </c>
@@ -4658,11 +4785,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N32" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N32" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>767</v>
       </c>
@@ -4707,11 +4838,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N33" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N33" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>767</v>
       </c>
@@ -4756,11 +4891,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N34" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N34" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>767</v>
       </c>
@@ -4805,11 +4944,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N35" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N35" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>767</v>
       </c>
@@ -4854,11 +4997,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N36" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N36" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>767</v>
       </c>
@@ -4903,11 +5050,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N37" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N37" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>767</v>
       </c>
@@ -4952,11 +5103,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N38" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>767</v>
       </c>
@@ -5001,11 +5156,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N39" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>767</v>
       </c>
@@ -5050,11 +5209,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N40" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N40" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>767</v>
       </c>
@@ -5099,11 +5262,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N41" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N41" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>763</v>
       </c>
@@ -5148,11 +5315,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N42" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N42" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>765</v>
       </c>
@@ -5197,11 +5368,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N43" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N43" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>765</v>
       </c>
@@ -5246,11 +5421,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N44" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N44" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>765</v>
       </c>
@@ -5295,11 +5474,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N45" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N45" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>765</v>
       </c>
@@ -5344,11 +5527,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N46" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N46" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>766</v>
       </c>
@@ -5393,11 +5580,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N47" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N47" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>766</v>
       </c>
@@ -5442,11 +5633,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N48" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N48" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>767</v>
       </c>
@@ -5491,11 +5686,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N49" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N49" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>767</v>
       </c>
@@ -5540,11 +5739,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N50" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N50" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>767</v>
       </c>
@@ -5589,11 +5792,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N51" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N51" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>766</v>
       </c>
@@ -5638,11 +5845,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N52" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N52" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>767</v>
       </c>
@@ -5687,11 +5898,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N53" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N53" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>766</v>
       </c>
@@ -5736,11 +5951,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N54" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N54" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>766</v>
       </c>
@@ -5785,11 +6004,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N55" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N55" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>762</v>
       </c>
@@ -5834,11 +6057,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N56" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N56" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>762</v>
       </c>
@@ -5883,11 +6110,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N57" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N57" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>762</v>
       </c>
@@ -5932,11 +6163,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N58" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N58" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>762</v>
       </c>
@@ -5981,11 +6216,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N59" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N59" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>762</v>
       </c>
@@ -6030,11 +6269,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N60" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N60" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>762</v>
       </c>
@@ -6079,11 +6322,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N61" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N61" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>763</v>
       </c>
@@ -6128,11 +6375,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N62" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N62" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>763</v>
       </c>
@@ -6177,11 +6428,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N63" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N63" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>763</v>
       </c>
@@ -6226,11 +6481,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N64" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N64" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>763</v>
       </c>
@@ -6275,11 +6534,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N65" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N65" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>763</v>
       </c>
@@ -6324,11 +6587,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N66" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N66" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>765</v>
       </c>
@@ -6373,11 +6640,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N67" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N67" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>766</v>
       </c>
@@ -6422,11 +6693,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N68" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N68" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>766</v>
       </c>
@@ -6471,11 +6746,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N69" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N69" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>767</v>
       </c>
@@ -6520,11 +6799,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N70" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N70" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>767</v>
       </c>
@@ -6569,11 +6852,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N71" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N71" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>767</v>
       </c>
@@ -6618,11 +6905,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N72" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N72" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>767</v>
       </c>
@@ -6667,11 +6958,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N73" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N73" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>767</v>
       </c>
@@ -6716,11 +7011,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N74" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N74" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>767</v>
       </c>
@@ -6765,11 +7064,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N75" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N75" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>767</v>
       </c>
@@ -6814,11 +7117,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N76" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N76" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>763</v>
       </c>
@@ -6863,11 +7170,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N77" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N77" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>763</v>
       </c>
@@ -6912,11 +7223,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N78" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N78" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>763</v>
       </c>
@@ -6961,11 +7276,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N79" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N79" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>763</v>
       </c>
@@ -7010,11 +7329,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N80" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>764</v>
       </c>
@@ -7059,11 +7382,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N81" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N81" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>765</v>
       </c>
@@ -7108,11 +7435,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N82" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N82" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>767</v>
       </c>
@@ -7157,11 +7488,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N83" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N83" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>767</v>
       </c>
@@ -7206,11 +7541,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N84" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N84" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>767</v>
       </c>
@@ -7255,11 +7594,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N85" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N85" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>762</v>
       </c>
@@ -7304,11 +7647,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N86" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N86" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>762</v>
       </c>
@@ -7353,11 +7700,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N87" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N87" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>762</v>
       </c>
@@ -7402,11 +7753,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N88" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N88" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>762</v>
       </c>
@@ -7451,11 +7806,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N89" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N89" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>762</v>
       </c>
@@ -7500,11 +7859,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N90" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N90" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>762</v>
       </c>
@@ -7549,11 +7912,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N91" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N91" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>762</v>
       </c>
@@ -7598,11 +7965,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N92" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N92" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>762</v>
       </c>
@@ -7647,11 +8018,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N93" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N93" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>762</v>
       </c>
@@ -7696,11 +8071,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N94" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N94" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>762</v>
       </c>
@@ -7745,11 +8124,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N95" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N95" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>763</v>
       </c>
@@ -7794,11 +8177,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N96" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N96" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>763</v>
       </c>
@@ -7843,11 +8230,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N97" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N97" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>763</v>
       </c>
@@ -7892,11 +8283,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N98" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N98" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>763</v>
       </c>
@@ -7941,11 +8336,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N99" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N99" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>763</v>
       </c>
@@ -7990,11 +8389,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N100" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N100" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>763</v>
       </c>
@@ -8039,11 +8442,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N101" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N101" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>765</v>
       </c>
@@ -8088,11 +8495,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N102" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N102" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>767</v>
       </c>
@@ -8137,11 +8548,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N103" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N103" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>764</v>
       </c>
@@ -8186,11 +8601,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N104" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N104" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>762</v>
       </c>
@@ -8235,11 +8654,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N105" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N105" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>762</v>
       </c>
@@ -8284,11 +8707,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N106" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N106" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>762</v>
       </c>
@@ -8333,11 +8760,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N107" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N107" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>762</v>
       </c>
@@ -8382,11 +8813,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N108" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>762</v>
       </c>
@@ -8431,11 +8866,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N109" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N109" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>762</v>
       </c>
@@ -8480,11 +8919,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N110" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N110" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>762</v>
       </c>
@@ -8529,11 +8972,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N111" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N111" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>763</v>
       </c>
@@ -8578,11 +9025,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N112" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N112" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>763</v>
       </c>
@@ -8627,11 +9078,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N113" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N113" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>763</v>
       </c>
@@ -8676,11 +9131,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N114" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N114" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>763</v>
       </c>
@@ -8725,11 +9184,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N115" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N115" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>764</v>
       </c>
@@ -8774,11 +9237,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N116" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N116" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>764</v>
       </c>
@@ -8823,11 +9290,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N117" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N117" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>765</v>
       </c>
@@ -8872,11 +9343,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N118" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N118" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>765</v>
       </c>
@@ -8921,11 +9396,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N119" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>767</v>
       </c>
@@ -8970,11 +9449,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N120" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N120" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>767</v>
       </c>
@@ -9019,11 +9502,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N121" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N121" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>767</v>
       </c>
@@ -9068,11 +9555,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N122" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N122" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>767</v>
       </c>
@@ -9117,11 +9608,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N123" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N123" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>767</v>
       </c>
@@ -9166,11 +9661,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N124" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N124" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>767</v>
       </c>
@@ -9215,11 +9714,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N125" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N125" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O125" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>767</v>
       </c>
@@ -9264,11 +9767,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N126" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>767</v>
       </c>
@@ -9313,11 +9820,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N127" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N127" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>767</v>
       </c>
@@ -9362,11 +9873,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N128" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N128" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>767</v>
       </c>
@@ -9411,11 +9926,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N129" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N129" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O129" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>767</v>
       </c>
@@ -9460,11 +9979,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N130" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N130" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>767</v>
       </c>
@@ -9509,11 +10032,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N131" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N131" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O131" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>767</v>
       </c>
@@ -9558,11 +10085,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N132" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N132" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>763</v>
       </c>
@@ -9607,11 +10138,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N133" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N133" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>765</v>
       </c>
@@ -9656,11 +10191,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N134" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N134" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O134" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>765</v>
       </c>
@@ -9705,11 +10244,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N135" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N135" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>765</v>
       </c>
@@ -9754,11 +10297,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N136" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N136" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O136" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>767</v>
       </c>
@@ -9803,11 +10350,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N137" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N137" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O137" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>767</v>
       </c>
@@ -9852,11 +10403,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N138" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N138" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O138" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>762</v>
       </c>
@@ -9901,11 +10456,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N139" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N139" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O139" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>762</v>
       </c>
@@ -9950,11 +10509,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N140" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N140" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>763</v>
       </c>
@@ -9999,11 +10562,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N141" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N141" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O141" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>763</v>
       </c>
@@ -10048,11 +10615,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N142" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N142" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O142" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>763</v>
       </c>
@@ -10097,11 +10668,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N143" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>763</v>
       </c>
@@ -10146,11 +10721,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N144" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N144" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O144" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>767</v>
       </c>
@@ -10195,11 +10774,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N145" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N145" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>767</v>
       </c>
@@ -10244,11 +10827,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N146" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N146" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>767</v>
       </c>
@@ -10293,11 +10880,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N147" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N147" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O147" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>763</v>
       </c>
@@ -10342,11 +10933,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N148" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N148" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O148" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>763</v>
       </c>
@@ -10391,11 +10986,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N149" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N149" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O149" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>763</v>
       </c>
@@ -10440,11 +11039,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N150" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N150" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O150" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>763</v>
       </c>
@@ -10489,11 +11092,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N151" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N151" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O151" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>767</v>
       </c>
@@ -10538,11 +11145,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N152" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N152" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>767</v>
       </c>
@@ -10587,11 +11198,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N153" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N153" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O153" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>767</v>
       </c>
@@ -10636,11 +11251,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N154" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N154" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O154" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>762</v>
       </c>
@@ -10685,11 +11304,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N155" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N155" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O155" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>762</v>
       </c>
@@ -10734,11 +11357,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N156" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N156" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O156" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>762</v>
       </c>
@@ -10783,11 +11410,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N157" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N157" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O157" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>762</v>
       </c>
@@ -10832,11 +11463,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N158" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N158" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O158" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>762</v>
       </c>
@@ -10881,11 +11516,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N159" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N159" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O159" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>762</v>
       </c>
@@ -10930,11 +11569,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N160" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N160" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O160" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>762</v>
       </c>
@@ -10979,11 +11622,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N161" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N161" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O161" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>762</v>
       </c>
@@ -11028,11 +11675,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N162" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N162" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O162" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>762</v>
       </c>
@@ -11077,11 +11728,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N163" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N163" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O163" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>767</v>
       </c>
@@ -11126,11 +11781,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N164" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N164" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O164" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>764</v>
       </c>
@@ -11175,11 +11834,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N165" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N165" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O165" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>763</v>
       </c>
@@ -11224,11 +11887,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N166" t="s">
+      <c r="N166" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O166" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>767</v>
       </c>
@@ -11267,17 +11934,21 @@
         <v>318</v>
       </c>
       <c r="L167" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="M167" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N167" t="s">
+      <c r="N167" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O167" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>766</v>
       </c>
@@ -11316,17 +11987,21 @@
         <v>321</v>
       </c>
       <c r="L168" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="M168" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N168" t="s">
+      <c r="N168" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O168" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>766</v>
       </c>
@@ -11365,17 +12040,21 @@
         <v>60</v>
       </c>
       <c r="L169" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="M169" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N169" t="s">
+      <c r="N169" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O169" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>765</v>
       </c>
@@ -11414,17 +12093,21 @@
         <v>318</v>
       </c>
       <c r="L170" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M170" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N170" t="s">
+      <c r="N170" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O170" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>765</v>
       </c>
@@ -11463,17 +12146,21 @@
         <v>328</v>
       </c>
       <c r="L171" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="M171" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N171" t="s">
+      <c r="N171" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O171" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>765</v>
       </c>
@@ -11512,17 +12199,21 @@
         <v>318</v>
       </c>
       <c r="L172" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="M172" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N172" t="s">
+      <c r="N172" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O172" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>767</v>
       </c>
@@ -11561,17 +12252,21 @@
         <v>333</v>
       </c>
       <c r="L173" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="M173" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N173" t="s">
+      <c r="N173" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O173" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>767</v>
       </c>
@@ -11610,17 +12305,21 @@
         <v>333</v>
       </c>
       <c r="L174" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="M174" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N174" t="s">
+      <c r="N174" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O174" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>764</v>
       </c>
@@ -11659,17 +12358,21 @@
         <v>18</v>
       </c>
       <c r="L175" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="M175" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N175" t="s">
+      <c r="N175" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O175" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>766</v>
       </c>
@@ -11708,17 +12411,21 @@
         <v>340</v>
       </c>
       <c r="L176" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="M176" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N176" t="s">
+      <c r="N176" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>766</v>
       </c>
@@ -11757,17 +12464,21 @@
         <v>340</v>
       </c>
       <c r="L177" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="M177" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N177" t="s">
+      <c r="N177" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O177" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>767</v>
       </c>
@@ -11812,11 +12523,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N178" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N178" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O178" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>763</v>
       </c>
@@ -11861,11 +12576,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N179" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N179" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O179" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>762</v>
       </c>
@@ -11910,11 +12629,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N180" t="s">
+      <c r="N180" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O180" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>762</v>
       </c>
@@ -11953,17 +12676,21 @@
         <v>9</v>
       </c>
       <c r="L181" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="M181" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N181" t="s">
+      <c r="N181" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O181" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>762</v>
       </c>
@@ -12008,11 +12735,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N182" t="s">
+      <c r="N182" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O182" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>762</v>
       </c>
@@ -12057,11 +12788,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N183" t="s">
+      <c r="N183" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O183" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>763</v>
       </c>
@@ -12106,11 +12841,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N184" t="s">
+      <c r="N184" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O184" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>763</v>
       </c>
@@ -12149,17 +12888,21 @@
         <v>357</v>
       </c>
       <c r="L185" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="M185" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N185" t="s">
+      <c r="N185" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O185" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>763</v>
       </c>
@@ -12198,17 +12941,21 @@
         <v>156</v>
       </c>
       <c r="L186" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="M186" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N186" t="s">
+      <c r="N186" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O186" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>763</v>
       </c>
@@ -12253,11 +13000,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N187" t="s">
+      <c r="N187" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O187" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>764</v>
       </c>
@@ -12302,11 +13053,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N188" t="s">
+      <c r="N188" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O188" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>764</v>
       </c>
@@ -12345,17 +13100,21 @@
         <v>363</v>
       </c>
       <c r="L189" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="M189" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N189" t="s">
+      <c r="N189" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O189" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>765</v>
       </c>
@@ -12394,17 +13153,21 @@
         <v>318</v>
       </c>
       <c r="L190" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="M190" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N190" t="s">
+      <c r="N190" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O190" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>765</v>
       </c>
@@ -12443,17 +13206,21 @@
         <v>318</v>
       </c>
       <c r="L191" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="M191" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N191" t="s">
+      <c r="N191" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O191" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>765</v>
       </c>
@@ -12498,11 +13265,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N192" t="s">
+      <c r="N192" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>765</v>
       </c>
@@ -12547,11 +13318,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N193" t="s">
+      <c r="N193" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O193" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>766</v>
       </c>
@@ -12596,11 +13371,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N194" t="s">
+      <c r="N194" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O194" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>767</v>
       </c>
@@ -12645,11 +13424,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N195" t="s">
+      <c r="N195" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O195" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>767</v>
       </c>
@@ -12694,11 +13477,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N196" t="s">
+      <c r="N196" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O196" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>767</v>
       </c>
@@ -12737,17 +13524,21 @@
         <v>318</v>
       </c>
       <c r="L197" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="M197" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N197" t="s">
+      <c r="N197" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O197" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>767</v>
       </c>
@@ -12786,17 +13577,21 @@
         <v>318</v>
       </c>
       <c r="L198" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="M198" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N198" t="s">
+      <c r="N198" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O198" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>763</v>
       </c>
@@ -12835,17 +13630,21 @@
         <v>363</v>
       </c>
       <c r="L199" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M199" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N199" t="s">
+      <c r="N199" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O199" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>764</v>
       </c>
@@ -12884,17 +13683,21 @@
         <v>363</v>
       </c>
       <c r="L200" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="M200" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N200" t="s">
+      <c r="N200" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O200" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>764</v>
       </c>
@@ -12933,17 +13736,21 @@
         <v>363</v>
       </c>
       <c r="L201" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="M201" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N201" t="s">
+      <c r="N201" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O201" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>764</v>
       </c>
@@ -12982,17 +13789,21 @@
         <v>363</v>
       </c>
       <c r="L202" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="M202" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N202" t="s">
+      <c r="N202" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O202" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>765</v>
       </c>
@@ -13031,17 +13842,21 @@
         <v>328</v>
       </c>
       <c r="L203" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="M203" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N203" t="s">
+      <c r="N203" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O203" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>765</v>
       </c>
@@ -13080,17 +13895,21 @@
         <v>328</v>
       </c>
       <c r="L204" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="M204" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N204" t="s">
+      <c r="N204" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O204" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>765</v>
       </c>
@@ -13129,17 +13948,21 @@
         <v>12</v>
       </c>
       <c r="L205" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M205" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N205" t="s">
+      <c r="N205" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O205" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>765</v>
       </c>
@@ -13178,17 +14001,21 @@
         <v>333</v>
       </c>
       <c r="L206" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M206" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N206" t="s">
+      <c r="N206" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O206" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>765</v>
       </c>
@@ -13227,17 +14054,21 @@
         <v>333</v>
       </c>
       <c r="L207" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="M207" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N207" t="s">
+      <c r="N207" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O207" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>767</v>
       </c>
@@ -13276,17 +14107,21 @@
         <v>375</v>
       </c>
       <c r="L208" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="M208" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N208" t="s">
+      <c r="N208" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O208" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>767</v>
       </c>
@@ -13325,17 +14160,21 @@
         <v>318</v>
       </c>
       <c r="L209" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="M209" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N209" t="s">
+      <c r="N209" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O209" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>762</v>
       </c>
@@ -13380,11 +14219,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N210" t="s">
+      <c r="N210" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O210" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>762</v>
       </c>
@@ -13423,17 +14266,21 @@
         <v>9</v>
       </c>
       <c r="L211" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="M211" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N211" t="s">
+      <c r="N211" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O211" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>762</v>
       </c>
@@ -13478,11 +14325,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N212" t="s">
+      <c r="N212" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O212" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>762</v>
       </c>
@@ -13527,11 +14378,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N213" t="s">
+      <c r="N213" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O213" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>763</v>
       </c>
@@ -13576,11 +14431,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N214" t="s">
+      <c r="N214" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O214" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>763</v>
       </c>
@@ -13619,17 +14478,21 @@
         <v>357</v>
       </c>
       <c r="L215" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="M215" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N215" t="s">
+      <c r="N215" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O215" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>763</v>
       </c>
@@ -13668,17 +14531,21 @@
         <v>156</v>
       </c>
       <c r="L216" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="M216" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N216" t="s">
+      <c r="N216" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O216" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>763</v>
       </c>
@@ -13723,11 +14590,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N217" t="s">
+      <c r="N217" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O217" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>764</v>
       </c>
@@ -13772,11 +14643,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N218" t="s">
+      <c r="N218" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O218" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>764</v>
       </c>
@@ -13815,17 +14690,21 @@
         <v>363</v>
       </c>
       <c r="L219" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="M219" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N219" t="s">
+      <c r="N219" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O219" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>765</v>
       </c>
@@ -13864,17 +14743,21 @@
         <v>318</v>
       </c>
       <c r="L220" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="M220" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N220" t="s">
+      <c r="N220" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O220" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>765</v>
       </c>
@@ -13913,17 +14796,21 @@
         <v>318</v>
       </c>
       <c r="L221" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="M221" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N221" t="s">
+      <c r="N221" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O221" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>765</v>
       </c>
@@ -13968,11 +14855,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N222" t="s">
+      <c r="N222" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>765</v>
       </c>
@@ -14017,11 +14908,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N223" t="s">
+      <c r="N223" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O223" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>766</v>
       </c>
@@ -14066,11 +14961,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N224" t="s">
+      <c r="N224" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O224" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>767</v>
       </c>
@@ -14115,11 +15014,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N225" t="s">
+      <c r="N225" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O225" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>767</v>
       </c>
@@ -14164,11 +15067,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N226" t="s">
+      <c r="N226" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O226" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>767</v>
       </c>
@@ -14207,17 +15114,21 @@
         <v>318</v>
       </c>
       <c r="L227" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="M227" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N227" t="s">
+      <c r="N227" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O227" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>767</v>
       </c>
@@ -14256,17 +15167,21 @@
         <v>318</v>
       </c>
       <c r="L228" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="M228" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N228" t="s">
+      <c r="N228" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O228" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>763</v>
       </c>
@@ -14305,17 +15220,21 @@
         <v>363</v>
       </c>
       <c r="L229" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M229" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N229" t="s">
+      <c r="N229" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O229" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>762</v>
       </c>
@@ -14360,11 +15279,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N230" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N230" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O230" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>764</v>
       </c>
@@ -14403,17 +15326,21 @@
         <v>363</v>
       </c>
       <c r="L231" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="M231" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N231" t="s">
+      <c r="N231" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O231" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>764</v>
       </c>
@@ -14452,17 +15379,21 @@
         <v>363</v>
       </c>
       <c r="L232" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="M232" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N232" t="s">
+      <c r="N232" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O232" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>765</v>
       </c>
@@ -14501,17 +15432,21 @@
         <v>328</v>
       </c>
       <c r="L233" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="M233" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N233" t="s">
+      <c r="N233" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O233" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>765</v>
       </c>
@@ -14550,17 +15485,21 @@
         <v>328</v>
       </c>
       <c r="L234" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="M234" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N234" t="s">
+      <c r="N234" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O234" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>765</v>
       </c>
@@ -14599,17 +15538,21 @@
         <v>12</v>
       </c>
       <c r="L235" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M235" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N235" t="s">
+      <c r="N235" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O235" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>765</v>
       </c>
@@ -14648,17 +15591,21 @@
         <v>333</v>
       </c>
       <c r="L236" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M236" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N236" t="s">
+      <c r="N236" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O236" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>765</v>
       </c>
@@ -14697,17 +15644,21 @@
         <v>333</v>
       </c>
       <c r="L237" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="M237" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N237" t="s">
+      <c r="N237" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O237" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>767</v>
       </c>
@@ -14746,17 +15697,21 @@
         <v>375</v>
       </c>
       <c r="L238" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="M238" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N238" t="s">
+      <c r="N238" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O238" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>767</v>
       </c>
@@ -14795,17 +15750,21 @@
         <v>318</v>
       </c>
       <c r="L239" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="M239" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N239" t="s">
+      <c r="N239" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O239" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>762</v>
       </c>
@@ -14844,17 +15803,21 @@
         <v>12</v>
       </c>
       <c r="L240" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="M240" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N240" t="s">
+      <c r="N240" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O240" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>762</v>
       </c>
@@ -14893,17 +15856,21 @@
         <v>9</v>
       </c>
       <c r="L241" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="M241" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N241" t="s">
+      <c r="N241" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O241" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>763</v>
       </c>
@@ -14942,17 +15909,21 @@
         <v>363</v>
       </c>
       <c r="L242" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="M242" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N242" t="s">
+      <c r="N242" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O242" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>765</v>
       </c>
@@ -14997,11 +15968,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N243" t="s">
+      <c r="N243" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O243" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>765</v>
       </c>
@@ -15040,17 +16015,21 @@
         <v>55</v>
       </c>
       <c r="L244" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="M244" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N244" t="s">
+      <c r="N244" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O244" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>766</v>
       </c>
@@ -15089,17 +16068,21 @@
         <v>321</v>
       </c>
       <c r="L245" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M245" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N245" t="s">
+      <c r="N245" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O245" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>766</v>
       </c>
@@ -15138,17 +16121,21 @@
         <v>321</v>
       </c>
       <c r="L246" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M246" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N246" t="s">
+      <c r="N246" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O246" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>766</v>
       </c>
@@ -15187,17 +16174,21 @@
         <v>321</v>
       </c>
       <c r="L247" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="M247" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N247" t="s">
+      <c r="N247" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O247" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>766</v>
       </c>
@@ -15236,17 +16227,21 @@
         <v>340</v>
       </c>
       <c r="L248" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="M248" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N248" t="s">
+      <c r="N248" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O248" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>766</v>
       </c>
@@ -15291,11 +16286,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N249" t="s">
+      <c r="N249" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O249" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>766</v>
       </c>
@@ -15334,17 +16333,21 @@
         <v>321</v>
       </c>
       <c r="L250" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="M250" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N250" t="s">
+      <c r="N250" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O250" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>766</v>
       </c>
@@ -15383,17 +16386,21 @@
         <v>321</v>
       </c>
       <c r="L251" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M251" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N251" t="s">
+      <c r="N251" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O251" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>766</v>
       </c>
@@ -15432,17 +16439,21 @@
         <v>321</v>
       </c>
       <c r="L252" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="M252" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N252" t="s">
+      <c r="N252" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O252" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>767</v>
       </c>
@@ -15481,17 +16492,21 @@
         <v>318</v>
       </c>
       <c r="L253" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="M253" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N253" t="s">
+      <c r="N253" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O253" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>762</v>
       </c>
@@ -15530,17 +16545,21 @@
         <v>12</v>
       </c>
       <c r="L254" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M254" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N254" t="s">
+      <c r="N254" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O254" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>762</v>
       </c>
@@ -15579,17 +16598,21 @@
         <v>12</v>
       </c>
       <c r="L255" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="M255" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N255" t="s">
+      <c r="N255" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O255" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>762</v>
       </c>
@@ -15628,17 +16651,21 @@
         <v>60</v>
       </c>
       <c r="L256" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="M256" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N256" t="s">
+      <c r="N256" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O256" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>762</v>
       </c>
@@ -15677,17 +16704,21 @@
         <v>12</v>
       </c>
       <c r="L257" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="M257" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N257" t="s">
+      <c r="N257" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O257" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>763</v>
       </c>
@@ -15726,17 +16757,21 @@
         <v>357</v>
       </c>
       <c r="L258" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="M258" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N258" t="s">
+      <c r="N258" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O258" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>763</v>
       </c>
@@ -15775,17 +16810,21 @@
         <v>156</v>
       </c>
       <c r="L259" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="M259" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N259" t="s">
+      <c r="N259" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O259" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>763</v>
       </c>
@@ -15824,17 +16863,21 @@
         <v>156</v>
       </c>
       <c r="L260" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="M260" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N260" t="s">
+      <c r="N260" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O260" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>763</v>
       </c>
@@ -15873,17 +16916,21 @@
         <v>156</v>
       </c>
       <c r="L261" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="M261" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N261" t="s">
+      <c r="N261" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O261" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>763</v>
       </c>
@@ -15922,17 +16969,21 @@
         <v>357</v>
       </c>
       <c r="L262" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="M262" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N262" t="s">
+      <c r="N262" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O262" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>763</v>
       </c>
@@ -15971,17 +17022,21 @@
         <v>156</v>
       </c>
       <c r="L263" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="M263" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N263" t="s">
+      <c r="N263" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O263" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>764</v>
       </c>
@@ -16020,17 +17075,21 @@
         <v>363</v>
       </c>
       <c r="L264" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="M264" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N264" t="s">
+      <c r="N264" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O264" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>764</v>
       </c>
@@ -16069,17 +17128,21 @@
         <v>363</v>
       </c>
       <c r="L265" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="M265" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N265" t="s">
+      <c r="N265" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O265" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>764</v>
       </c>
@@ -16118,17 +17181,21 @@
         <v>18</v>
       </c>
       <c r="L266" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="M266" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N266" t="s">
+      <c r="N266" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O266" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>764</v>
       </c>
@@ -16167,17 +17234,21 @@
         <v>363</v>
       </c>
       <c r="L267" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M267" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N267" t="s">
+      <c r="N267" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O267" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>764</v>
       </c>
@@ -16216,17 +17287,21 @@
         <v>363</v>
       </c>
       <c r="L268" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="M268" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N268" t="s">
+      <c r="N268" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O268" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>764</v>
       </c>
@@ -16265,17 +17340,21 @@
         <v>363</v>
       </c>
       <c r="L269" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="M269" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N269" t="s">
+      <c r="N269" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O269" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>764</v>
       </c>
@@ -16314,17 +17393,21 @@
         <v>363</v>
       </c>
       <c r="L270" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="M270" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N270" t="s">
+      <c r="N270" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O270" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>765</v>
       </c>
@@ -16363,17 +17446,21 @@
         <v>333</v>
       </c>
       <c r="L271" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="M271" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N271" t="s">
+      <c r="N271" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O271" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>765</v>
       </c>
@@ -16412,17 +17499,21 @@
         <v>318</v>
       </c>
       <c r="L272" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M272" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N272" t="s">
+      <c r="N272" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O272" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>765</v>
       </c>
@@ -16461,17 +17552,21 @@
         <v>328</v>
       </c>
       <c r="L273" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="M273" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N273" t="s">
+      <c r="N273" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O273" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>765</v>
       </c>
@@ -16510,17 +17605,21 @@
         <v>328</v>
       </c>
       <c r="L274" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="M274" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N274" t="s">
+      <c r="N274" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O274" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>765</v>
       </c>
@@ -16559,17 +17658,21 @@
         <v>318</v>
       </c>
       <c r="L275" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M275" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N275" t="s">
+      <c r="N275" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O275" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>765</v>
       </c>
@@ -16608,17 +17711,21 @@
         <v>328</v>
       </c>
       <c r="L276" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M276" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N276" t="s">
+      <c r="N276" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O276" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>765</v>
       </c>
@@ -16657,17 +17764,21 @@
         <v>328</v>
       </c>
       <c r="L277" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="M277" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N277" t="s">
+      <c r="N277" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O277" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>765</v>
       </c>
@@ -16706,17 +17817,21 @@
         <v>328</v>
       </c>
       <c r="L278" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="M278" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N278" t="s">
+      <c r="N278" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O278" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>765</v>
       </c>
@@ -16755,17 +17870,21 @@
         <v>363</v>
       </c>
       <c r="L279" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="M279" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N279" t="s">
+      <c r="N279" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O279" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>766</v>
       </c>
@@ -16804,17 +17923,21 @@
         <v>321</v>
       </c>
       <c r="L280" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="M280" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N280" t="s">
+      <c r="N280" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O280" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>766</v>
       </c>
@@ -16853,17 +17976,21 @@
         <v>321</v>
       </c>
       <c r="L281" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="M281" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N281" t="s">
+      <c r="N281" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O281" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>766</v>
       </c>
@@ -16902,17 +18029,21 @@
         <v>321</v>
       </c>
       <c r="L282" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="M282" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N282" t="s">
+      <c r="N282" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O282" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>766</v>
       </c>
@@ -16951,17 +18082,21 @@
         <v>321</v>
       </c>
       <c r="L283" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="M283" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N283" t="s">
+      <c r="N283" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O283" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>766</v>
       </c>
@@ -17000,17 +18135,21 @@
         <v>340</v>
       </c>
       <c r="L284" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M284" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N284" t="s">
+      <c r="N284" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O284" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>766</v>
       </c>
@@ -17049,17 +18188,21 @@
         <v>340</v>
       </c>
       <c r="L285" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M285" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N285" t="s">
+      <c r="N285" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O285" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>766</v>
       </c>
@@ -17098,17 +18241,21 @@
         <v>321</v>
       </c>
       <c r="L286" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M286" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N286" t="s">
+      <c r="N286" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O286" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>766</v>
       </c>
@@ -17147,17 +18294,21 @@
         <v>321</v>
       </c>
       <c r="L287" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="M287" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N287" t="s">
+      <c r="N287" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O287" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>766</v>
       </c>
@@ -17196,17 +18347,21 @@
         <v>321</v>
       </c>
       <c r="L288" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="M288" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N288" t="s">
+      <c r="N288" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O288" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>766</v>
       </c>
@@ -17245,17 +18400,21 @@
         <v>60</v>
       </c>
       <c r="L289" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="M289" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N289" t="s">
+      <c r="N289" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O289" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>766</v>
       </c>
@@ -17294,17 +18453,21 @@
         <v>321</v>
       </c>
       <c r="L290" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="M290" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N290" t="s">
+      <c r="N290" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O290" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>766</v>
       </c>
@@ -17343,17 +18506,21 @@
         <v>321</v>
       </c>
       <c r="L291" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="M291" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N291" t="s">
+      <c r="N291" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O291" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>766</v>
       </c>
@@ -17392,17 +18559,21 @@
         <v>321</v>
       </c>
       <c r="L292" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="M292" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N292" t="s">
+      <c r="N292" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O292" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>766</v>
       </c>
@@ -17441,17 +18612,21 @@
         <v>321</v>
       </c>
       <c r="L293" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="M293" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N293" t="s">
+      <c r="N293" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O293" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>767</v>
       </c>
@@ -17490,17 +18665,21 @@
         <v>89</v>
       </c>
       <c r="L294" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M294" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N294" t="s">
+      <c r="N294" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O294" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>767</v>
       </c>
@@ -17539,17 +18718,21 @@
         <v>318</v>
       </c>
       <c r="L295" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="M295" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N295" t="s">
+      <c r="N295" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O295" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>767</v>
       </c>
@@ -17588,17 +18771,21 @@
         <v>58</v>
       </c>
       <c r="L296" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="M296" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N296" t="s">
+      <c r="N296" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O296" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>767</v>
       </c>
@@ -17637,17 +18824,21 @@
         <v>318</v>
       </c>
       <c r="L297" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="M297" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N297" t="s">
+      <c r="N297" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O297" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>767</v>
       </c>
@@ -17686,17 +18877,21 @@
         <v>89</v>
       </c>
       <c r="L298" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="M298" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N298" t="s">
+      <c r="N298" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O298" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>767</v>
       </c>
@@ -17735,17 +18930,21 @@
         <v>318</v>
       </c>
       <c r="L299" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="M299" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N299" t="s">
+      <c r="N299" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O299" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>763</v>
       </c>
@@ -17784,17 +18983,21 @@
         <v>156</v>
       </c>
       <c r="L300" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="M300" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N300" t="s">
+      <c r="N300" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O300" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>763</v>
       </c>
@@ -17833,17 +19036,21 @@
         <v>156</v>
       </c>
       <c r="L301" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="M301" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N301" t="s">
+      <c r="N301" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O301" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>766</v>
       </c>
@@ -17882,17 +19089,21 @@
         <v>60</v>
       </c>
       <c r="L302" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="M302" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N302" t="s">
+      <c r="N302" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O302" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>763</v>
       </c>
@@ -17931,17 +19142,21 @@
         <v>355</v>
       </c>
       <c r="L303" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M303" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N303" t="s">
+      <c r="N303" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O303" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>762</v>
       </c>
@@ -17980,17 +19195,21 @@
         <v>9</v>
       </c>
       <c r="L304" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="M304" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N304" t="s">
+      <c r="N304" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O304" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>762</v>
       </c>
@@ -18029,17 +19248,21 @@
         <v>22</v>
       </c>
       <c r="L305" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M305" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N305" t="s">
+      <c r="N305" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O305" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>762</v>
       </c>
@@ -18078,17 +19301,21 @@
         <v>9</v>
       </c>
       <c r="L306" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="M306" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N306" t="s">
+      <c r="N306" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O306" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>762</v>
       </c>
@@ -18127,17 +19354,21 @@
         <v>9</v>
       </c>
       <c r="L307" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="M307" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N307" t="s">
+      <c r="N307" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O307" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>762</v>
       </c>
@@ -18176,17 +19407,21 @@
         <v>22</v>
       </c>
       <c r="L308" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M308" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N308" t="s">
+      <c r="N308" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O308" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>762</v>
       </c>
@@ -18225,17 +19460,21 @@
         <v>22</v>
       </c>
       <c r="L309" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="M309" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N309" t="s">
+      <c r="N309" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O309" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>762</v>
       </c>
@@ -18274,17 +19513,21 @@
         <v>9</v>
       </c>
       <c r="L310" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="M310" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N310" t="s">
+      <c r="N310" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O310" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>763</v>
       </c>
@@ -18323,17 +19566,21 @@
         <v>9</v>
       </c>
       <c r="L311" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="M311" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N311" t="s">
+      <c r="N311" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O311" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>763</v>
       </c>
@@ -18372,17 +19619,21 @@
         <v>9</v>
       </c>
       <c r="L312" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="M312" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N312" t="s">
+      <c r="N312" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O312" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>765</v>
       </c>
@@ -18421,17 +19672,21 @@
         <v>55</v>
       </c>
       <c r="L313" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="M313" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N313" t="s">
+      <c r="N313" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O313" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>762</v>
       </c>
@@ -18476,11 +19731,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N314" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N314" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O314" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>762</v>
       </c>
@@ -18525,11 +19784,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N315" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N315" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O315" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>762</v>
       </c>
@@ -18574,11 +19837,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N316" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N316" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O316" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>762</v>
       </c>
@@ -18623,11 +19890,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N317" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N317" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O317" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>762</v>
       </c>
@@ -18672,11 +19943,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N318" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N318" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O318" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>767</v>
       </c>
@@ -18721,11 +19996,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N319" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N319" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O319" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>767</v>
       </c>
@@ -18770,11 +20049,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N320" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N320" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O320" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>763</v>
       </c>
@@ -18819,11 +20102,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N321" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N321" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O321" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>762</v>
       </c>
@@ -18868,11 +20155,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N322" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N322" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O322" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>767</v>
       </c>
@@ -18917,11 +20208,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N323" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N323" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O323" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>767</v>
       </c>
@@ -18966,11 +20261,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N324" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N324" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O324" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>767</v>
       </c>
@@ -19015,11 +20314,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N325" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N325" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O325" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>767</v>
       </c>
@@ -19064,11 +20367,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N326" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N326" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O326" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>762</v>
       </c>
@@ -19113,11 +20420,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N327" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N327" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O327" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>763</v>
       </c>
@@ -19162,11 +20473,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N328" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N328" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O328" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>762</v>
       </c>
@@ -19211,11 +20526,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N329" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N329" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O329" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>762</v>
       </c>
@@ -19260,11 +20579,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N330" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N330" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O330" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>762</v>
       </c>
@@ -19309,11 +20632,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N331" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N331" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O331" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>767</v>
       </c>
@@ -19358,11 +20685,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N332" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N332" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O332" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>763</v>
       </c>
@@ -19407,11 +20738,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N333" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N333" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O333" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>763</v>
       </c>
@@ -19456,11 +20791,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N334" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N334" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O334" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>763</v>
       </c>
@@ -19505,11 +20844,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N335" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N335" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O335" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>767</v>
       </c>
@@ -19554,11 +20897,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N336" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N336" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O336" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>767</v>
       </c>
@@ -19603,11 +20950,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N337" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N337" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O337" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>763</v>
       </c>
@@ -19652,11 +21003,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N338" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N338" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O338" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>763</v>
       </c>
@@ -19701,11 +21056,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N339" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N339" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O339" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>767</v>
       </c>
@@ -19750,11 +21109,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N340" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N340" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O340" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>767</v>
       </c>
@@ -19799,11 +21162,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N341" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N341" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O341" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>767</v>
       </c>
@@ -19848,11 +21215,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N342" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N342" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O342" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>767</v>
       </c>
@@ -19897,11 +21268,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N343" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N343" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O343" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>767</v>
       </c>
@@ -19946,11 +21321,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N344" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N344" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O344" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>767</v>
       </c>
@@ -19995,11 +21374,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N345" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N345" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O345" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>767</v>
       </c>
@@ -20044,11 +21427,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N346" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N346" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O346" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>767</v>
       </c>
@@ -20093,11 +21480,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N347" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N347" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O347" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>767</v>
       </c>
@@ -20142,11 +21533,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N348" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N348" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O348" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>767</v>
       </c>
@@ -20191,11 +21586,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N349" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N349" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O349" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>767</v>
       </c>
@@ -20240,11 +21639,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N350" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N350" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O350" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>767</v>
       </c>
@@ -20289,11 +21692,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N351" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N351" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O351" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>767</v>
       </c>
@@ -20338,11 +21745,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N352" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N352" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O352" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>767</v>
       </c>
@@ -20387,11 +21798,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N353" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N353" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O353" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>767</v>
       </c>
@@ -20436,11 +21851,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N354" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N354" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O354" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>767</v>
       </c>
@@ -20485,11 +21904,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N355" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N355" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O355" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>767</v>
       </c>
@@ -20534,11 +21957,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N356" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N356" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O356" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>767</v>
       </c>
@@ -20583,11 +22010,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N357" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N357" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O357" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>764</v>
       </c>
@@ -20632,11 +22063,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N358" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N358" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O358" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>765</v>
       </c>
@@ -20681,11 +22116,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N359" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N359" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O359" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>765</v>
       </c>
@@ -20730,11 +22169,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N360" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N360" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O360" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>765</v>
       </c>
@@ -20779,11 +22222,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N361" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N361" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O361" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>764</v>
       </c>
@@ -20828,11 +22275,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N362" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N362" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O362" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>766</v>
       </c>
@@ -20877,11 +22328,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N363" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N363" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O363" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>766</v>
       </c>
@@ -20926,11 +22381,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N364" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N364" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O364" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>763</v>
       </c>
@@ -20975,11 +22434,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N365" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N365" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O365" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>763</v>
       </c>
@@ -21024,11 +22487,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N366" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N366" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O366" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>763</v>
       </c>
@@ -21073,11 +22540,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N367" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N367" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O367" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>763</v>
       </c>
@@ -21122,11 +22593,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N368" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N368" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O368" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>764</v>
       </c>
@@ -21171,11 +22646,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N369" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N369" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O369" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>764</v>
       </c>
@@ -21220,11 +22699,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N370" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N370" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O370" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>764</v>
       </c>
@@ -21269,11 +22752,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N371" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N371" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O371" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>764</v>
       </c>
@@ -21318,11 +22805,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N372" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N372" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O372" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>762</v>
       </c>
@@ -21367,11 +22858,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N373" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N373" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O373" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>762</v>
       </c>
@@ -21416,11 +22911,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N374" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N374" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O374" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>762</v>
       </c>
@@ -21465,11 +22964,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N375" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N375" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O375" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>762</v>
       </c>
@@ -21514,11 +23017,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N376" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N376" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O376" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>762</v>
       </c>
@@ -21563,11 +23070,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N377" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N377" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O377" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>762</v>
       </c>
@@ -21612,11 +23123,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N378" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N378" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O378" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>762</v>
       </c>
@@ -21661,11 +23176,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N379" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N379" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O379" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>762</v>
       </c>
@@ -21710,11 +23229,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N380" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N380" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O380" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>762</v>
       </c>
@@ -21759,11 +23282,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N381" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N381" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O381" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>762</v>
       </c>
@@ -21808,11 +23335,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N382" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N382" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O382" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>762</v>
       </c>
@@ -21857,11 +23388,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N383" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N383" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O383" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>764</v>
       </c>
@@ -21906,11 +23441,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N384" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N384" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O384" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>766</v>
       </c>
@@ -21955,11 +23494,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N385" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N385" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O385" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>766</v>
       </c>
@@ -22004,11 +23547,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N386" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N386" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O386" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>766</v>
       </c>
@@ -22053,11 +23600,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N387" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N387" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O387" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>766</v>
       </c>
@@ -22102,11 +23653,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N388" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N388" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O388" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>766</v>
       </c>
@@ -22151,11 +23706,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N389" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N389" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O389" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>766</v>
       </c>
@@ -22200,11 +23759,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N390" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N390" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O390" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>766</v>
       </c>
@@ -22249,11 +23812,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N391" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N391" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O391" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>766</v>
       </c>
@@ -22298,11 +23865,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N392" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N392" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O392" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>762</v>
       </c>
@@ -22347,11 +23918,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N393" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N393" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O393" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>762</v>
       </c>
@@ -22396,11 +23971,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N394" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N394" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O394" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>762</v>
       </c>
@@ -22445,11 +24024,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N395" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N395" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O395" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>762</v>
       </c>
@@ -22494,11 +24077,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N396" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N396" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O396" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>762</v>
       </c>
@@ -22543,11 +24130,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N397" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N397" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O397" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>762</v>
       </c>
@@ -22592,11 +24183,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N398" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N398" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O398" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>762</v>
       </c>
@@ -22641,11 +24236,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N399" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N399" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O399" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>762</v>
       </c>
@@ -22690,11 +24289,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N400" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N400" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O400" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>762</v>
       </c>
@@ -22739,11 +24342,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N401" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N401" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O401" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>762</v>
       </c>
@@ -22788,11 +24395,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N402" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N402" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O402" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>762</v>
       </c>
@@ -22837,11 +24448,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N403" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N403" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O403" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>762</v>
       </c>
@@ -22886,11 +24501,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N404" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N404" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O404" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>762</v>
       </c>
@@ -22935,11 +24554,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N405" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N405" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O405" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>762</v>
       </c>
@@ -22984,11 +24607,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N406" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N406" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O406" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>762</v>
       </c>
@@ -23033,11 +24660,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N407" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N407" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O407" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>762</v>
       </c>
@@ -23082,11 +24713,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N408" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N408" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O408" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>766</v>
       </c>
@@ -23131,11 +24766,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N409" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N409" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O409" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>766</v>
       </c>
@@ -23180,11 +24819,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N410" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N410" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O410" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>766</v>
       </c>
@@ -23229,11 +24872,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N411" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N411" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O411" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>764</v>
       </c>
@@ -23278,11 +24925,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N412" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N412" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O412" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>764</v>
       </c>
@@ -23327,11 +24978,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N413" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N413" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O413" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>764</v>
       </c>
@@ -23376,11 +25031,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N414" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N414" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O414" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>766</v>
       </c>
@@ -23425,11 +25084,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N415" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N415" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O415" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>766</v>
       </c>
@@ -23474,11 +25137,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N416" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N416" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O416" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>766</v>
       </c>
@@ -23523,11 +25190,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N417" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N417" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O417" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>767</v>
       </c>
@@ -23572,11 +25243,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N418" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N418" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O418" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>763</v>
       </c>
@@ -23621,11 +25296,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N419" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N419" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O419" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>765</v>
       </c>
@@ -23670,11 +25349,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N420" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N420" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O420" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>767</v>
       </c>
@@ -23719,11 +25402,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N421" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N421" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O421" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>767</v>
       </c>
@@ -23768,11 +25455,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N422" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N422" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O422" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>767</v>
       </c>
@@ -23817,11 +25508,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N423" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N423" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O423" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>762</v>
       </c>
@@ -23866,11 +25561,15 @@
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="N424" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N424" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O424" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>762</v>
       </c>
@@ -23915,11 +25614,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N425" s="4" t="s">
+      <c r="N425" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O425" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>762</v>
       </c>
@@ -23964,11 +25667,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N426" s="4" t="s">
+      <c r="N426" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O426" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>762</v>
       </c>
@@ -24013,11 +25720,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N427" s="4" t="s">
+      <c r="N427" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O427" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>763</v>
       </c>
@@ -24062,11 +25773,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N428" s="4" t="s">
+      <c r="N428" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O428" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>763</v>
       </c>
@@ -24111,11 +25826,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N429" s="4" t="s">
+      <c r="N429" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O429" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>764</v>
       </c>
@@ -24160,11 +25879,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N430" s="4" t="s">
+      <c r="N430" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O430" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>765</v>
       </c>
@@ -24209,11 +25932,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N431" s="4" t="s">
+      <c r="N431" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O431" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>765</v>
       </c>
@@ -24258,11 +25985,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N432" s="4" t="s">
+      <c r="N432" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O432" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>765</v>
       </c>
@@ -24307,11 +26038,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N433" s="4" t="s">
+      <c r="N433" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O433" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>766</v>
       </c>
@@ -24356,11 +26091,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N434" s="4" t="s">
+      <c r="N434" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O434" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>766</v>
       </c>
@@ -24405,11 +26144,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N435" s="4" t="s">
+      <c r="N435" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O435" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>767</v>
       </c>
@@ -24454,11 +26197,15 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N436" s="4" t="s">
+      <c r="N436" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O436" s="4" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>767</v>
       </c>
@@ -24503,12 +26250,16 @@
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="N437" s="4" t="s">
+      <c r="N437" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="O437" s="4" t="s">
         <v>757</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N437" xr:uid="{949F7AB2-2F55-43AE-8970-69B0FC61725F}"/>
+  <autoFilter ref="A1:O437" xr:uid="{949F7AB2-2F55-43AE-8970-69B0FC61725F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri"&amp;11&amp;K5C2D91 This message/document has been classified as “Internal”&amp;1#_x000D_</oddHeader>

--- a/backend/data/map_v4.6.xlsx
+++ b/backend/data/map_v4.6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fahmy\PycharmProjects\syncDashboard\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA85542-9876-48E8-90B8-04F39DEAEEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA77BB0C-C605-4655-A89D-F3AB36CD65F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58F0FD76-519D-46BD-9AA4-233998471043}"/>
   </bookViews>
@@ -3170,8 +3170,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="b">
         <f>FALSE</f>
@@ -3223,8 +3222,7 @@
         <v>74</v>
       </c>
       <c r="G3" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3" t="b">
         <f>FALSE</f>
@@ -3276,7 +3274,6 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H4" s="3" t="b">
@@ -3329,8 +3326,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="b">
         <f>FALSE</f>
@@ -3382,7 +3378,6 @@
         <v>84</v>
       </c>
       <c r="G6" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H6" s="3" t="b">
@@ -3435,8 +3430,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="b">
         <f>FALSE</f>
@@ -3488,8 +3482,7 @@
         <v>62</v>
       </c>
       <c r="G8" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3" t="b">
         <f>FALSE</f>
@@ -3541,7 +3534,6 @@
         <v>175</v>
       </c>
       <c r="G9" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H9" s="3" t="b">
@@ -3594,7 +3586,6 @@
         <v>17</v>
       </c>
       <c r="G10" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H10" s="3" t="b">
@@ -3647,7 +3638,6 @@
         <v>2</v>
       </c>
       <c r="G11" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H11" s="3" t="b">
@@ -3700,8 +3690,7 @@
         <v>33</v>
       </c>
       <c r="G12" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3" t="b">
         <f>FALSE</f>
@@ -3753,7 +3742,6 @@
         <v>26</v>
       </c>
       <c r="G13" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H13" s="3" t="b">
@@ -3806,7 +3794,6 @@
         <v>2</v>
       </c>
       <c r="G14" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H14" s="3" t="b">
@@ -3859,8 +3846,7 @@
         <v>61</v>
       </c>
       <c r="G15" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="b">
         <f>FALSE</f>
@@ -3912,8 +3898,7 @@
         <v>39</v>
       </c>
       <c r="G16" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="3" t="b">
         <f>FALSE</f>
@@ -3965,8 +3950,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="3" t="b">
         <f>FALSE</f>
@@ -4018,8 +4002,7 @@
         <v>25</v>
       </c>
       <c r="G18" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="3" t="b">
         <f>FALSE</f>
@@ -4071,7 +4054,6 @@
         <v>14</v>
       </c>
       <c r="G19" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H19" s="3" t="b">
@@ -4124,7 +4106,6 @@
         <v>85</v>
       </c>
       <c r="G20" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H20" s="3" t="b">
@@ -4177,7 +4158,6 @@
         <v>63</v>
       </c>
       <c r="G21" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H21" s="3" t="b">
@@ -4230,7 +4210,6 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H22" s="3" t="b">
@@ -4283,8 +4262,7 @@
         <v>136</v>
       </c>
       <c r="G23" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3" t="b">
         <f>FALSE</f>
@@ -4336,8 +4314,7 @@
         <v>47</v>
       </c>
       <c r="G24" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="b">
         <f>FALSE</f>
@@ -4389,8 +4366,7 @@
         <v>29</v>
       </c>
       <c r="G25" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="3" t="b">
         <f>FALSE</f>
@@ -4442,8 +4418,7 @@
         <v>41</v>
       </c>
       <c r="G26" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3" t="b">
         <f>FALSE</f>
@@ -4495,8 +4470,7 @@
         <v>2</v>
       </c>
       <c r="G27" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="b">
         <f>FALSE</f>
@@ -4548,7 +4522,6 @@
         <v>1</v>
       </c>
       <c r="G28" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H28" s="3" t="b">
@@ -4601,8 +4574,7 @@
         <v>69</v>
       </c>
       <c r="G29" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3" t="b">
         <f>FALSE</f>
@@ -4654,7 +4626,6 @@
         <v>175</v>
       </c>
       <c r="G30" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H30" s="3" t="b">
@@ -4707,8 +4678,7 @@
         <v>77</v>
       </c>
       <c r="G31" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="3" t="b">
         <f>FALSE</f>
@@ -4760,7 +4730,6 @@
         <v>126</v>
       </c>
       <c r="G32" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H32" s="3" t="b">
@@ -4813,8 +4782,7 @@
         <v>69</v>
       </c>
       <c r="G33" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="3" t="b">
         <f>FALSE</f>
@@ -4866,7 +4834,6 @@
         <v>96</v>
       </c>
       <c r="G34" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H34" s="3" t="b">
@@ -4919,7 +4886,6 @@
         <v>12</v>
       </c>
       <c r="G35" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H35" s="3" t="b">
@@ -4972,7 +4938,6 @@
         <v>165</v>
       </c>
       <c r="G36" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H36" s="3" t="b">
@@ -5025,7 +4990,6 @@
         <v>13</v>
       </c>
       <c r="G37" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H37" s="3" t="b">
@@ -5078,7 +5042,6 @@
         <v>91</v>
       </c>
       <c r="G38" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H38" s="3" t="b">
@@ -5131,7 +5094,6 @@
         <v>65</v>
       </c>
       <c r="G39" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H39" s="3" t="b">
@@ -5184,8 +5146,7 @@
         <v>82</v>
       </c>
       <c r="G40" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="3" t="b">
         <f>FALSE</f>
@@ -5237,7 +5198,6 @@
         <v>14</v>
       </c>
       <c r="G41" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H41" s="3" t="b">
@@ -5290,8 +5250,7 @@
         <v>61</v>
       </c>
       <c r="G42" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3" t="b">
         <f>FALSE</f>
@@ -5343,8 +5302,7 @@
         <v>45</v>
       </c>
       <c r="G43" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="b">
         <f>FALSE</f>
@@ -5396,7 +5354,6 @@
         <v>2</v>
       </c>
       <c r="G44" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H44" s="3" t="b">
@@ -5449,8 +5406,7 @@
         <v>49</v>
       </c>
       <c r="G45" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3" t="b">
         <f>FALSE</f>
@@ -5502,8 +5458,7 @@
         <v>75</v>
       </c>
       <c r="G46" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="3" t="b">
         <f>FALSE</f>
@@ -5555,7 +5510,6 @@
         <v>27</v>
       </c>
       <c r="G47" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H47" s="3" t="b">
@@ -5608,8 +5562,7 @@
         <v>10</v>
       </c>
       <c r="G48" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="b">
         <f>FALSE</f>
@@ -5661,8 +5614,7 @@
         <v>14</v>
       </c>
       <c r="G49" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="3" t="b">
         <f>FALSE</f>
@@ -5714,8 +5666,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="3" t="b">
         <f>FALSE</f>
@@ -5767,7 +5718,6 @@
         <v>1</v>
       </c>
       <c r="G51" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H51" s="3" t="b">
@@ -5820,8 +5770,7 @@
         <v>25</v>
       </c>
       <c r="G52" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3" t="b">
         <f>FALSE</f>
@@ -5873,8 +5822,7 @@
         <v>29</v>
       </c>
       <c r="G53" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3" t="b">
         <f>FALSE</f>
@@ -5926,8 +5874,7 @@
         <v>11</v>
       </c>
       <c r="G54" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" s="3" t="b">
         <f>FALSE</f>
@@ -5979,8 +5926,7 @@
         <v>5</v>
       </c>
       <c r="G55" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="3" t="b">
         <f>FALSE</f>
@@ -6032,7 +5978,6 @@
         <v>79</v>
       </c>
       <c r="G56" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H56" s="3" t="b">
@@ -6085,7 +6030,6 @@
         <v>0</v>
       </c>
       <c r="G57" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H57" s="3" t="b">
@@ -6138,7 +6082,6 @@
         <v>48</v>
       </c>
       <c r="G58" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H58" s="3" t="b">
@@ -6191,7 +6134,6 @@
         <v>6</v>
       </c>
       <c r="G59" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H59" s="3" t="b">
@@ -6244,7 +6186,6 @@
         <v>23</v>
       </c>
       <c r="G60" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H60" s="3" t="b">
@@ -6297,7 +6238,6 @@
         <v>0</v>
       </c>
       <c r="G61" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H61" s="3" t="b">
@@ -6350,8 +6290,7 @@
         <v>82</v>
       </c>
       <c r="G62" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3" t="b">
         <f>FALSE</f>
@@ -6403,8 +6342,7 @@
         <v>70</v>
       </c>
       <c r="G63" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="3" t="b">
         <f>FALSE</f>
@@ -6456,8 +6394,7 @@
         <v>85</v>
       </c>
       <c r="G64" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="3" t="b">
         <f>FALSE</f>
@@ -6509,8 +6446,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="3" t="b">
         <f>FALSE</f>
@@ -6562,7 +6498,6 @@
         <v>0</v>
       </c>
       <c r="G66" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H66" s="3" t="b">
@@ -6615,7 +6550,6 @@
         <v>2</v>
       </c>
       <c r="G67" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H67" s="3" t="b">
@@ -6668,8 +6602,7 @@
         <v>45</v>
       </c>
       <c r="G68" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="3" t="b">
         <f>FALSE</f>
@@ -6721,8 +6654,7 @@
         <v>53</v>
       </c>
       <c r="G69" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="3" t="b">
         <f>FALSE</f>
@@ -6774,7 +6706,6 @@
         <v>17</v>
       </c>
       <c r="G70" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H70" s="3" t="b">
@@ -6827,8 +6758,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="3" t="b">
         <f>FALSE</f>
@@ -6880,7 +6810,6 @@
         <v>4</v>
       </c>
       <c r="G72" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H72" s="3" t="b">
@@ -6933,7 +6862,6 @@
         <v>2</v>
       </c>
       <c r="G73" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H73" s="3" t="b">
@@ -6986,7 +6914,6 @@
         <v>0</v>
       </c>
       <c r="G74" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H74" s="3" t="b">
@@ -7039,7 +6966,6 @@
         <v>9</v>
       </c>
       <c r="G75" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H75" s="3" t="b">
@@ -7092,7 +7018,6 @@
         <v>4</v>
       </c>
       <c r="G76" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H76" s="3" t="b">
@@ -7145,7 +7070,6 @@
         <v>0</v>
       </c>
       <c r="G77" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H77" s="3" t="b">
@@ -7198,7 +7122,6 @@
         <v>16</v>
       </c>
       <c r="G78" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H78" s="3" t="b">
@@ -7251,7 +7174,6 @@
         <v>0</v>
       </c>
       <c r="G79" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H79" s="3" t="b">
@@ -7304,7 +7226,6 @@
         <v>0</v>
       </c>
       <c r="G80" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H80" s="3" t="b">
@@ -7357,8 +7278,7 @@
         <v>6</v>
       </c>
       <c r="G81" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3" t="b">
         <f>FALSE</f>
@@ -7410,7 +7330,6 @@
         <v>18</v>
       </c>
       <c r="G82" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H82" s="3" t="b">
@@ -7463,8 +7382,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="b">
         <f>FALSE</f>
@@ -7516,8 +7434,7 @@
         <v>18</v>
       </c>
       <c r="G84" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="3" t="b">
         <f>FALSE</f>
@@ -7569,8 +7486,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="3" t="b">
         <f>FALSE</f>
@@ -7622,8 +7538,7 @@
         <v>20</v>
       </c>
       <c r="G86" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="3" t="b">
         <f>FALSE</f>
@@ -7675,8 +7590,7 @@
         <v>73</v>
       </c>
       <c r="G87" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="3" t="b">
         <f>FALSE</f>
@@ -7728,8 +7642,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" s="3" t="b">
         <f>FALSE</f>
@@ -7781,7 +7694,6 @@
         <v>64</v>
       </c>
       <c r="G89" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H89" s="3" t="b">
@@ -7834,8 +7746,7 @@
         <v>33</v>
       </c>
       <c r="G90" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="3" t="b">
         <f>FALSE</f>
@@ -7887,8 +7798,7 @@
         <v>45</v>
       </c>
       <c r="G91" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="b">
         <f>FALSE</f>
@@ -7940,7 +7850,6 @@
         <v>39</v>
       </c>
       <c r="G92" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H92" s="3" t="b">
@@ -7993,8 +7902,7 @@
         <v>8</v>
       </c>
       <c r="G93" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="3" t="b">
         <f>FALSE</f>
@@ -8046,8 +7954,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="b">
         <f>FALSE</f>
@@ -8099,8 +8006,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="3" t="b">
         <f>FALSE</f>
@@ -8152,8 +8058,7 @@
         <v>27</v>
       </c>
       <c r="G96" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3" t="b">
         <f>FALSE</f>
@@ -8205,7 +8110,6 @@
         <v>30</v>
       </c>
       <c r="G97" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H97" s="3" t="b">
@@ -8258,8 +8162,7 @@
         <v>9</v>
       </c>
       <c r="G98" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="3" t="b">
         <f>FALSE</f>
@@ -8311,8 +8214,7 @@
         <v>8</v>
       </c>
       <c r="G99" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="3" t="b">
         <f>FALSE</f>
@@ -8364,8 +8266,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="3" t="b">
         <f>FALSE</f>
@@ -8417,8 +8318,7 @@
         <v>52</v>
       </c>
       <c r="G101" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="3" t="b">
         <f>FALSE</f>
@@ -8470,7 +8370,6 @@
         <v>7</v>
       </c>
       <c r="G102" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H102" s="3" t="b">
@@ -8523,7 +8422,6 @@
         <v>0</v>
       </c>
       <c r="G103" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H103" s="3" t="b">
@@ -8576,8 +8474,7 @@
         <v>15</v>
       </c>
       <c r="G104" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" s="3" t="b">
         <f>FALSE</f>
@@ -8629,7 +8526,6 @@
         <v>19</v>
       </c>
       <c r="G105" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H105" s="3" t="b">
@@ -8682,8 +8578,7 @@
         <v>185</v>
       </c>
       <c r="G106" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="3" t="b">
         <f>FALSE</f>
@@ -8735,7 +8630,6 @@
         <v>128</v>
       </c>
       <c r="G107" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H107" s="3" t="b">
@@ -8788,7 +8682,6 @@
         <v>174</v>
       </c>
       <c r="G108" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H108" s="3" t="b">
@@ -8841,8 +8734,7 @@
         <v>100</v>
       </c>
       <c r="G109" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="3" t="b">
         <f>FALSE</f>
@@ -8894,8 +8786,7 @@
         <v>51</v>
       </c>
       <c r="G110" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="3" t="b">
         <f>FALSE</f>
@@ -8947,8 +8838,7 @@
         <v>122</v>
       </c>
       <c r="G111" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="3" t="b">
         <f>FALSE</f>
@@ -9000,7 +8890,6 @@
         <v>84</v>
       </c>
       <c r="G112" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H112" s="3" t="b">
@@ -9053,7 +8942,6 @@
         <v>50</v>
       </c>
       <c r="G113" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H113" s="3" t="b">
@@ -9106,8 +8994,7 @@
         <v>99</v>
       </c>
       <c r="G114" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="3" t="b">
         <f>FALSE</f>
@@ -9159,7 +9046,6 @@
         <v>72</v>
       </c>
       <c r="G115" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H115" s="3" t="b">
@@ -9212,7 +9098,6 @@
         <v>52</v>
       </c>
       <c r="G116" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H116" s="3" t="b">
@@ -9265,7 +9150,6 @@
         <v>77</v>
       </c>
       <c r="G117" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H117" s="3" t="b">
@@ -9318,8 +9202,7 @@
         <v>69</v>
       </c>
       <c r="G118" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="3" t="b">
         <f>FALSE</f>
@@ -9371,7 +9254,6 @@
         <v>0</v>
       </c>
       <c r="G119" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H119" s="3" t="b">
@@ -9424,8 +9306,7 @@
         <v>10</v>
       </c>
       <c r="G120" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="3" t="b">
         <f>FALSE</f>
@@ -9477,8 +9358,7 @@
         <v>66</v>
       </c>
       <c r="G121" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" s="3" t="b">
         <f>FALSE</f>
@@ -9530,7 +9410,6 @@
         <v>115</v>
       </c>
       <c r="G122" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H122" s="3" t="b">
@@ -9583,8 +9462,7 @@
         <v>1</v>
       </c>
       <c r="G123" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="3" t="b">
         <f>FALSE</f>
@@ -9636,7 +9514,6 @@
         <v>23</v>
       </c>
       <c r="G124" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H124" s="3" t="b">
@@ -9689,7 +9566,6 @@
         <v>3</v>
       </c>
       <c r="G125" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H125" s="3" t="b">
@@ -9742,7 +9618,6 @@
         <v>1</v>
       </c>
       <c r="G126" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H126" s="3" t="b">
@@ -9795,7 +9670,6 @@
         <v>65</v>
       </c>
       <c r="G127" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H127" s="3" t="b">
@@ -9848,8 +9722,7 @@
         <v>322</v>
       </c>
       <c r="G128" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" s="3" t="b">
         <f>FALSE</f>
@@ -9901,7 +9774,6 @@
         <v>45</v>
       </c>
       <c r="G129" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H129" s="3" t="b">
@@ -9954,7 +9826,6 @@
         <v>29</v>
       </c>
       <c r="G130" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H130" s="3" t="b">
@@ -10007,7 +9878,6 @@
         <v>8</v>
       </c>
       <c r="G131" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H131" s="3" t="b">
@@ -10060,7 +9930,6 @@
         <v>8</v>
       </c>
       <c r="G132" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H132" s="3" t="b">
@@ -10113,8 +9982,7 @@
         <v>14</v>
       </c>
       <c r="G133" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" s="3" t="b">
         <f>FALSE</f>
@@ -10166,8 +10034,7 @@
         <v>58</v>
       </c>
       <c r="G134" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134" s="3" t="b">
         <f>FALSE</f>
@@ -10219,7 +10086,6 @@
         <v>41</v>
       </c>
       <c r="G135" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H135" s="3" t="b">
@@ -10272,8 +10138,7 @@
         <v>53</v>
       </c>
       <c r="G136" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H136" s="3" t="b">
         <f>FALSE</f>
@@ -10325,7 +10190,6 @@
         <v>116</v>
       </c>
       <c r="G137" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H137" s="3" t="b">
@@ -10378,8 +10242,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" s="3" t="b">
         <f>FALSE</f>
@@ -10431,7 +10294,6 @@
         <v>47</v>
       </c>
       <c r="G139" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H139" s="3" t="b">
@@ -10484,7 +10346,6 @@
         <v>117</v>
       </c>
       <c r="G140" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H140" s="3" t="b">
@@ -10537,8 +10398,7 @@
         <v>0</v>
       </c>
       <c r="G141" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="3" t="b">
         <f>FALSE</f>
@@ -10590,8 +10450,7 @@
         <v>48</v>
       </c>
       <c r="G142" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="3" t="b">
         <f>FALSE</f>
@@ -10643,8 +10502,7 @@
         <v>44</v>
       </c>
       <c r="G143" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="3" t="b">
         <f>FALSE</f>
@@ -10696,7 +10554,6 @@
         <v>0</v>
       </c>
       <c r="G144" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H144" s="3" t="b">
@@ -10749,8 +10606,7 @@
         <v>1</v>
       </c>
       <c r="G145" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" s="3" t="b">
         <f>FALSE</f>
@@ -10802,8 +10658,7 @@
         <v>25</v>
       </c>
       <c r="G146" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="3" t="b">
         <f>FALSE</f>
@@ -10855,7 +10710,6 @@
         <v>77</v>
       </c>
       <c r="G147" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H147" s="3" t="b">
@@ -10908,7 +10762,6 @@
         <v>35</v>
       </c>
       <c r="G148" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H148" s="3" t="b">
@@ -10961,7 +10814,6 @@
         <v>7</v>
       </c>
       <c r="G149" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H149" s="3" t="b">
@@ -11014,7 +10866,6 @@
         <v>33</v>
       </c>
       <c r="G150" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H150" s="3" t="b">
@@ -11067,7 +10918,6 @@
         <v>0</v>
       </c>
       <c r="G151" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H151" s="3" t="b">
@@ -11120,8 +10970,7 @@
         <v>7</v>
       </c>
       <c r="G152" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H152" s="3" t="b">
         <f>FALSE</f>
@@ -11173,8 +11022,7 @@
         <v>91</v>
       </c>
       <c r="G153" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" s="3" t="b">
         <f>FALSE</f>
@@ -11226,8 +11074,7 @@
         <v>0</v>
       </c>
       <c r="G154" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154" s="3" t="b">
         <f>FALSE</f>
@@ -11279,8 +11126,7 @@
         <v>73</v>
       </c>
       <c r="G155" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" s="3" t="b">
         <f>FALSE</f>
@@ -11332,8 +11178,7 @@
         <v>37</v>
       </c>
       <c r="G156" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" s="3" t="b">
         <f>FALSE</f>
@@ -11385,8 +11230,7 @@
         <v>96</v>
       </c>
       <c r="G157" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157" s="3" t="b">
         <f>FALSE</f>
@@ -11438,7 +11282,6 @@
         <v>75</v>
       </c>
       <c r="G158" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H158" s="3" t="b">
@@ -11491,8 +11334,7 @@
         <v>37</v>
       </c>
       <c r="G159" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159" s="3" t="b">
         <f>FALSE</f>
@@ -11544,8 +11386,7 @@
         <v>46</v>
       </c>
       <c r="G160" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H160" s="3" t="b">
         <f>FALSE</f>
@@ -11597,8 +11438,7 @@
         <v>112</v>
       </c>
       <c r="G161" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161" s="3" t="b">
         <f>FALSE</f>
@@ -11650,8 +11490,7 @@
         <v>0</v>
       </c>
       <c r="G162" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" s="3" t="b">
         <f>FALSE</f>
@@ -11703,8 +11542,7 @@
         <v>0</v>
       </c>
       <c r="G163" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" s="3" t="b">
         <f>FALSE</f>
@@ -11756,7 +11594,6 @@
         <v>0</v>
       </c>
       <c r="G164" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H164" s="3" t="b">
@@ -11809,7 +11646,6 @@
         <v>42</v>
       </c>
       <c r="G165" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H165" s="3" t="b">
@@ -11862,8 +11698,7 @@
         <v>6</v>
       </c>
       <c r="G166" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="3" t="b">
         <f>FALSE</f>
@@ -11915,8 +11750,7 @@
         <v>1</v>
       </c>
       <c r="G167" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" s="3" t="b">
         <f>FALSE</f>
@@ -11968,7 +11802,6 @@
         <v>9</v>
       </c>
       <c r="G168" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H168" s="3" t="b">
@@ -12021,7 +11854,6 @@
         <v>0</v>
       </c>
       <c r="G169" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H169" s="3" t="b">
@@ -12074,8 +11906,7 @@
         <v>0</v>
       </c>
       <c r="G170" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H170" s="3" t="b">
         <f>FALSE</f>
@@ -12127,7 +11958,6 @@
         <v>0</v>
       </c>
       <c r="G171" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H171" s="3" t="b">
@@ -12180,8 +12010,7 @@
         <v>7</v>
       </c>
       <c r="G172" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" s="3" t="b">
         <f>FALSE</f>
@@ -12233,7 +12062,6 @@
         <v>8</v>
       </c>
       <c r="G173" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H173" s="3" t="b">
@@ -12286,7 +12114,6 @@
         <v>2</v>
       </c>
       <c r="G174" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H174" s="3" t="b">
@@ -12339,7 +12166,6 @@
         <v>5</v>
       </c>
       <c r="G175" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H175" s="3" t="b">
@@ -12392,7 +12218,6 @@
         <v>8</v>
       </c>
       <c r="G176" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H176" s="3" t="b">
@@ -12445,8 +12270,7 @@
         <v>9</v>
       </c>
       <c r="G177" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177" s="3" t="b">
         <f>FALSE</f>
@@ -12498,8 +12322,7 @@
         <v>0</v>
       </c>
       <c r="G178" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H178" s="3" t="b">
         <f>FALSE</f>
@@ -12551,8 +12374,7 @@
         <v>110</v>
       </c>
       <c r="G179" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179" s="3" t="b">
         <f>FALSE</f>
@@ -12604,7 +12426,6 @@
         <v>5</v>
       </c>
       <c r="G180" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H180" s="3" t="b">
@@ -12657,7 +12478,6 @@
         <v>116</v>
       </c>
       <c r="G181" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H181" s="3" t="b">
@@ -12710,7 +12530,6 @@
         <v>0</v>
       </c>
       <c r="G182" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H182" s="3" t="b">
@@ -12763,7 +12582,6 @@
         <v>0</v>
       </c>
       <c r="G183" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H183" s="3" t="b">
@@ -12816,7 +12634,6 @@
         <v>76</v>
       </c>
       <c r="G184" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H184" s="3" t="b">
@@ -12869,7 +12686,6 @@
         <v>0</v>
       </c>
       <c r="G185" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H185" s="3" t="b">
@@ -12922,8 +12738,7 @@
         <v>21</v>
       </c>
       <c r="G186" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H186" s="3" t="b">
         <f>FALSE</f>
@@ -12975,8 +12790,7 @@
         <v>0</v>
       </c>
       <c r="G187" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187" s="3" t="b">
         <f>FALSE</f>
@@ -13028,7 +12842,6 @@
         <v>72</v>
       </c>
       <c r="G188" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H188" s="3" t="b">
@@ -13081,7 +12894,6 @@
         <v>165</v>
       </c>
       <c r="G189" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H189" s="3" t="b">
@@ -13134,7 +12946,6 @@
         <v>72</v>
       </c>
       <c r="G190" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H190" s="3" t="b">
@@ -13187,7 +12998,6 @@
         <v>7</v>
       </c>
       <c r="G191" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H191" s="3" t="b">
@@ -13240,7 +13050,6 @@
         <v>70</v>
       </c>
       <c r="G192" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H192" s="3" t="b">
@@ -13293,7 +13102,6 @@
         <v>4</v>
       </c>
       <c r="G193" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H193" s="3" t="b">
@@ -13346,7 +13154,6 @@
         <v>126</v>
       </c>
       <c r="G194" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H194" s="3" t="b">
@@ -13399,7 +13206,6 @@
         <v>24</v>
       </c>
       <c r="G195" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H195" s="3" t="b">
@@ -13452,7 +13258,6 @@
         <v>0</v>
       </c>
       <c r="G196" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H196" s="3" t="b">
@@ -13505,7 +13310,6 @@
         <v>225</v>
       </c>
       <c r="G197" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H197" s="3" t="b">
@@ -13558,7 +13362,6 @@
         <v>97</v>
       </c>
       <c r="G198" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H198" s="3" t="b">
@@ -13611,7 +13414,6 @@
         <v>0</v>
       </c>
       <c r="G199" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H199" s="3" t="b">
@@ -13664,7 +13466,6 @@
         <v>2</v>
       </c>
       <c r="G200" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H200" s="3" t="b">
@@ -13717,8 +13518,7 @@
         <v>0</v>
       </c>
       <c r="G201" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H201" s="3" t="b">
         <f>FALSE</f>
@@ -13770,7 +13570,6 @@
         <v>0</v>
       </c>
       <c r="G202" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H202" s="3" t="b">
@@ -13823,7 +13622,6 @@
         <v>11</v>
       </c>
       <c r="G203" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H203" s="3" t="b">
@@ -13876,7 +13674,6 @@
         <v>8</v>
       </c>
       <c r="G204" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H204" s="3" t="b">
@@ -13929,7 +13726,6 @@
         <v>5</v>
       </c>
       <c r="G205" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H205" s="3" t="b">
@@ -13982,8 +13778,7 @@
         <v>1</v>
       </c>
       <c r="G206" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H206" s="3" t="b">
         <f>FALSE</f>
@@ -14035,8 +13830,7 @@
         <v>0</v>
       </c>
       <c r="G207" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H207" s="3" t="b">
         <f>FALSE</f>
@@ -14088,7 +13882,6 @@
         <v>0</v>
       </c>
       <c r="G208" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H208" s="3" t="b">
@@ -14141,7 +13934,6 @@
         <v>0</v>
       </c>
       <c r="G209" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H209" s="3" t="b">
@@ -14194,7 +13986,6 @@
         <v>154</v>
       </c>
       <c r="G210" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H210" s="3" t="b">
@@ -14247,7 +14038,6 @@
         <v>18</v>
       </c>
       <c r="G211" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H211" s="3" t="b">
@@ -14300,7 +14090,6 @@
         <v>0</v>
       </c>
       <c r="G212" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H212" s="3" t="b">
@@ -14353,7 +14142,6 @@
         <v>0</v>
       </c>
       <c r="G213" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H213" s="3" t="b">
@@ -14406,7 +14194,6 @@
         <v>58</v>
       </c>
       <c r="G214" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H214" s="3" t="b">
@@ -14459,7 +14246,6 @@
         <v>107</v>
       </c>
       <c r="G215" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H215" s="3" t="b">
@@ -14512,8 +14298,7 @@
         <v>47</v>
       </c>
       <c r="G216" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H216" s="3" t="b">
         <f>FALSE</f>
@@ -14565,8 +14350,7 @@
         <v>0</v>
       </c>
       <c r="G217" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217" s="3" t="b">
         <f>FALSE</f>
@@ -14618,7 +14402,6 @@
         <v>56</v>
       </c>
       <c r="G218" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H218" s="3" t="b">
@@ -14671,7 +14454,6 @@
         <v>56</v>
       </c>
       <c r="G219" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H219" s="3" t="b">
@@ -14724,7 +14506,6 @@
         <v>42</v>
       </c>
       <c r="G220" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H220" s="3" t="b">
@@ -14777,7 +14558,6 @@
         <v>5</v>
       </c>
       <c r="G221" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H221" s="3" t="b">
@@ -14830,7 +14610,6 @@
         <v>72</v>
       </c>
       <c r="G222" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H222" s="3" t="b">
@@ -14883,7 +14662,6 @@
         <v>108</v>
       </c>
       <c r="G223" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H223" s="3" t="b">
@@ -14936,7 +14714,6 @@
         <v>64</v>
       </c>
       <c r="G224" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H224" s="3" t="b">
@@ -14989,7 +14766,6 @@
         <v>44</v>
       </c>
       <c r="G225" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H225" s="3" t="b">
@@ -15042,7 +14818,6 @@
         <v>20</v>
       </c>
       <c r="G226" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H226" s="3" t="b">
@@ -15095,7 +14870,6 @@
         <v>47</v>
       </c>
       <c r="G227" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H227" s="3" t="b">
@@ -15148,7 +14922,6 @@
         <v>60</v>
       </c>
       <c r="G228" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H228" s="3" t="b">
@@ -15201,7 +14974,6 @@
         <v>22</v>
       </c>
       <c r="G229" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H229" s="3" t="b">
@@ -15254,8 +15026,7 @@
         <v>0</v>
       </c>
       <c r="G230" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H230" s="3" t="b">
         <f>FALSE</f>
@@ -15307,7 +15078,6 @@
         <v>6</v>
       </c>
       <c r="G231" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H231" s="3" t="b">
@@ -15360,7 +15130,6 @@
         <v>0</v>
       </c>
       <c r="G232" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H232" s="3" t="b">
@@ -15413,7 +15182,6 @@
         <v>77</v>
       </c>
       <c r="G233" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H233" s="3" t="b">
@@ -15466,7 +15234,6 @@
         <v>50</v>
       </c>
       <c r="G234" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H234" s="3" t="b">
@@ -15519,8 +15286,7 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235" s="3" t="b">
         <f>FALSE</f>
@@ -15572,7 +15338,6 @@
         <v>8</v>
       </c>
       <c r="G236" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H236" s="3" t="b">
@@ -15625,7 +15390,6 @@
         <v>36</v>
       </c>
       <c r="G237" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H237" s="3" t="b">
@@ -15678,7 +15442,6 @@
         <v>0</v>
       </c>
       <c r="G238" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H238" s="3" t="b">
@@ -15731,7 +15494,6 @@
         <v>0</v>
       </c>
       <c r="G239" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H239" s="3" t="b">
@@ -15784,7 +15546,6 @@
         <v>30</v>
       </c>
       <c r="G240" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H240" s="3" t="b">
@@ -15837,7 +15598,6 @@
         <v>35</v>
       </c>
       <c r="G241" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H241" s="3" t="b">
@@ -15890,7 +15650,6 @@
         <v>54</v>
       </c>
       <c r="G242" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H242" s="3" t="b">
@@ -15943,7 +15702,6 @@
         <v>89</v>
       </c>
       <c r="G243" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H243" s="3" t="b">
@@ -15996,7 +15754,6 @@
         <v>128</v>
       </c>
       <c r="G244" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H244" s="3" t="b">
@@ -16049,7 +15806,6 @@
         <v>68</v>
       </c>
       <c r="G245" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H245" s="3" t="b">
@@ -16102,7 +15858,6 @@
         <v>64</v>
       </c>
       <c r="G246" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H246" s="3" t="b">
@@ -16155,7 +15910,6 @@
         <v>52</v>
       </c>
       <c r="G247" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H247" s="3" t="b">
@@ -16208,7 +15962,6 @@
         <v>63</v>
       </c>
       <c r="G248" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H248" s="3" t="b">
@@ -16261,7 +16014,6 @@
         <v>124</v>
       </c>
       <c r="G249" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H249" s="3" t="b">
@@ -16314,7 +16066,6 @@
         <v>6</v>
       </c>
       <c r="G250" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H250" s="3" t="b">
@@ -16367,7 +16118,6 @@
         <v>55</v>
       </c>
       <c r="G251" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H251" s="3" t="b">
@@ -16420,7 +16170,6 @@
         <v>15</v>
       </c>
       <c r="G252" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H252" s="3" t="b">
@@ -16473,8 +16222,7 @@
         <v>2</v>
       </c>
       <c r="G253" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H253" s="3" t="b">
         <f>FALSE</f>
@@ -16526,7 +16274,6 @@
         <v>34</v>
       </c>
       <c r="G254" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H254" s="3" t="b">
@@ -16579,7 +16326,6 @@
         <v>22</v>
       </c>
       <c r="G255" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H255" s="3" t="b">
@@ -16632,7 +16378,6 @@
         <v>30</v>
       </c>
       <c r="G256" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H256" s="3" t="b">
@@ -16685,7 +16430,6 @@
         <v>0</v>
       </c>
       <c r="G257" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H257" s="3" t="b">
@@ -16738,7 +16482,6 @@
         <v>53</v>
       </c>
       <c r="G258" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H258" s="3" t="b">
@@ -16791,8 +16534,7 @@
         <v>35</v>
       </c>
       <c r="G259" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H259" s="3" t="b">
         <f>FALSE</f>
@@ -16844,8 +16586,7 @@
         <v>0</v>
       </c>
       <c r="G260" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H260" s="3" t="b">
         <f>FALSE</f>
@@ -16897,8 +16638,7 @@
         <v>42</v>
       </c>
       <c r="G261" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H261" s="3" t="b">
         <f>FALSE</f>
@@ -16950,7 +16690,6 @@
         <v>3</v>
       </c>
       <c r="G262" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H262" s="3" t="b">
@@ -17003,8 +16742,7 @@
         <v>25</v>
       </c>
       <c r="G263" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H263" s="3" t="b">
         <f>FALSE</f>
@@ -17056,8 +16794,7 @@
         <v>3</v>
       </c>
       <c r="G264" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" s="3" t="b">
         <f>FALSE</f>
@@ -17109,7 +16846,6 @@
         <v>42</v>
       </c>
       <c r="G265" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H265" s="3" t="b">
@@ -17162,7 +16898,6 @@
         <v>26</v>
       </c>
       <c r="G266" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H266" s="3" t="b">
@@ -17215,8 +16950,7 @@
         <v>0</v>
       </c>
       <c r="G267" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H267" s="3" t="b">
         <f>FALSE</f>
@@ -17268,7 +17002,6 @@
         <v>8</v>
       </c>
       <c r="G268" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H268" s="3" t="b">
@@ -17321,8 +17054,7 @@
         <v>7</v>
       </c>
       <c r="G269" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H269" s="3" t="b">
         <f>FALSE</f>
@@ -17374,7 +17106,6 @@
         <v>9</v>
       </c>
       <c r="G270" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H270" s="3" t="b">
@@ -17427,7 +17158,6 @@
         <v>107</v>
       </c>
       <c r="G271" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H271" s="3" t="b">
@@ -17480,7 +17210,6 @@
         <v>17</v>
       </c>
       <c r="G272" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H272" s="3" t="b">
@@ -17533,7 +17262,6 @@
         <v>54</v>
       </c>
       <c r="G273" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H273" s="3" t="b">
@@ -17586,7 +17314,6 @@
         <v>37</v>
       </c>
       <c r="G274" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H274" s="3" t="b">
@@ -17639,7 +17366,6 @@
         <v>5</v>
       </c>
       <c r="G275" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H275" s="3" t="b">
@@ -17692,7 +17418,6 @@
         <v>72</v>
       </c>
       <c r="G276" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H276" s="3" t="b">
@@ -17745,7 +17470,6 @@
         <v>21</v>
       </c>
       <c r="G277" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H277" s="3" t="b">
@@ -17798,7 +17522,6 @@
         <v>16</v>
       </c>
       <c r="G278" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H278" s="3" t="b">
@@ -17851,7 +17574,6 @@
         <v>3</v>
       </c>
       <c r="G279" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H279" s="3" t="b">
@@ -17904,7 +17626,6 @@
         <v>79</v>
       </c>
       <c r="G280" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H280" s="3" t="b">
@@ -17957,8 +17678,7 @@
         <v>1</v>
       </c>
       <c r="G281" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H281" s="3" t="b">
         <f>FALSE</f>
@@ -18010,7 +17730,6 @@
         <v>3</v>
       </c>
       <c r="G282" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H282" s="3" t="b">
@@ -18063,7 +17782,6 @@
         <v>3</v>
       </c>
       <c r="G283" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H283" s="3" t="b">
@@ -18116,7 +17834,6 @@
         <v>3</v>
       </c>
       <c r="G284" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H284" s="3" t="b">
@@ -18169,7 +17886,6 @@
         <v>0</v>
       </c>
       <c r="G285" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H285" s="3" t="b">
@@ -18222,7 +17938,6 @@
         <v>0</v>
       </c>
       <c r="G286" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H286" s="3" t="b">
@@ -18275,8 +17990,7 @@
         <v>9</v>
       </c>
       <c r="G287" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H287" s="3" t="b">
         <f>FALSE</f>
@@ -18328,7 +18042,6 @@
         <v>8</v>
       </c>
       <c r="G288" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H288" s="3" t="b">
@@ -18381,8 +18094,7 @@
         <v>0</v>
       </c>
       <c r="G289" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H289" s="3" t="b">
         <f>FALSE</f>
@@ -18434,7 +18146,6 @@
         <v>17</v>
       </c>
       <c r="G290" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H290" s="3" t="b">
@@ -18487,7 +18198,6 @@
         <v>5</v>
       </c>
       <c r="G291" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H291" s="3" t="b">
@@ -18540,7 +18250,6 @@
         <v>29</v>
       </c>
       <c r="G292" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H292" s="3" t="b">
@@ -18593,7 +18302,6 @@
         <v>6</v>
       </c>
       <c r="G293" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H293" s="3" t="b">
@@ -18646,7 +18354,6 @@
         <v>0</v>
       </c>
       <c r="G294" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H294" s="3" t="b">
@@ -18699,7 +18406,6 @@
         <v>27</v>
       </c>
       <c r="G295" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H295" s="3" t="b">
@@ -18752,7 +18458,6 @@
         <v>29</v>
       </c>
       <c r="G296" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H296" s="3" t="b">
@@ -18805,7 +18510,6 @@
         <v>18</v>
       </c>
       <c r="G297" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H297" s="3" t="b">
@@ -18858,7 +18562,6 @@
         <v>0</v>
       </c>
       <c r="G298" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H298" s="3" t="b">
@@ -18911,7 +18614,6 @@
         <v>5</v>
       </c>
       <c r="G299" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H299" s="3" t="b">
@@ -18964,8 +18666,7 @@
         <v>41</v>
       </c>
       <c r="G300" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H300" s="3" t="b">
         <f>FALSE</f>
@@ -19017,8 +18718,7 @@
         <v>15</v>
       </c>
       <c r="G301" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H301" s="3" t="b">
         <f>FALSE</f>
@@ -19070,7 +18770,6 @@
         <v>6</v>
       </c>
       <c r="G302" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H302" s="3" t="b">
@@ -19123,7 +18822,6 @@
         <v>10</v>
       </c>
       <c r="G303" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H303" s="3" t="b">
@@ -19176,8 +18874,7 @@
         <v>0</v>
       </c>
       <c r="G304" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" s="3" t="b">
         <f>FALSE</f>
@@ -19229,7 +18926,6 @@
         <v>24</v>
       </c>
       <c r="G305" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H305" s="3" t="b">
@@ -19282,7 +18978,6 @@
         <v>12</v>
       </c>
       <c r="G306" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H306" s="3" t="b">
@@ -19335,7 +19030,6 @@
         <v>21</v>
       </c>
       <c r="G307" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H307" s="3" t="b">
@@ -19388,7 +19082,6 @@
         <v>30</v>
       </c>
       <c r="G308" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H308" s="3" t="b">
@@ -19441,7 +19134,6 @@
         <v>9</v>
       </c>
       <c r="G309" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H309" s="3" t="b">
@@ -19494,8 +19186,7 @@
         <v>0</v>
       </c>
       <c r="G310" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H310" s="3" t="b">
         <f>FALSE</f>
@@ -19547,7 +19238,6 @@
         <v>13</v>
       </c>
       <c r="G311" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H311" s="3" t="b">
@@ -19600,7 +19290,6 @@
         <v>7</v>
       </c>
       <c r="G312" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H312" s="3" t="b">
@@ -19653,8 +19342,7 @@
         <v>3</v>
       </c>
       <c r="G313" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H313" s="3" t="b">
         <f>FALSE</f>
@@ -19706,8 +19394,7 @@
         <v>0</v>
       </c>
       <c r="G314" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H314" s="3" t="b">
         <f>FALSE</f>
@@ -19759,8 +19446,7 @@
         <v>1</v>
       </c>
       <c r="G315" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H315" s="3" t="b">
         <f>FALSE</f>
@@ -19812,8 +19498,7 @@
         <v>7</v>
       </c>
       <c r="G316" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H316" s="3" t="b">
         <f>FALSE</f>
@@ -19865,8 +19550,7 @@
         <v>0</v>
       </c>
       <c r="G317" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H317" s="3" t="b">
         <f>FALSE</f>
@@ -19918,8 +19602,7 @@
         <v>0</v>
       </c>
       <c r="G318" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H318" s="3" t="b">
         <f>FALSE</f>
@@ -19971,7 +19654,6 @@
         <v>5</v>
       </c>
       <c r="G319" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H319" s="3" t="b">
@@ -20024,7 +19706,6 @@
         <v>1</v>
       </c>
       <c r="G320" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H320" s="3" t="b">
@@ -20077,7 +19758,6 @@
         <v>3</v>
       </c>
       <c r="G321" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H321" s="3" t="b">
@@ -20130,8 +19810,7 @@
         <v>0</v>
       </c>
       <c r="G322" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H322" s="3" t="b">
         <f>FALSE</f>
@@ -20183,8 +19862,7 @@
         <v>0</v>
       </c>
       <c r="G323" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H323" s="3" t="b">
         <f>FALSE</f>
@@ -20236,7 +19914,6 @@
         <v>13</v>
       </c>
       <c r="G324" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H324" s="3" t="b">
@@ -20289,7 +19966,6 @@
         <v>0</v>
       </c>
       <c r="G325" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H325" s="3" t="b">
@@ -20342,7 +20018,6 @@
         <v>0</v>
       </c>
       <c r="G326" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H326" s="3" t="b">
@@ -20395,7 +20070,6 @@
         <v>1</v>
       </c>
       <c r="G327" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H327" s="3" t="b">
@@ -20448,7 +20122,6 @@
         <v>2</v>
       </c>
       <c r="G328" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H328" s="3" t="b">
@@ -20501,7 +20174,6 @@
         <v>2</v>
       </c>
       <c r="G329" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H329" s="3" t="b">
@@ -20554,7 +20226,6 @@
         <v>0</v>
       </c>
       <c r="G330" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H330" s="3" t="b">
@@ -20607,8 +20278,7 @@
         <v>15</v>
       </c>
       <c r="G331" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H331" s="3" t="b">
         <f>FALSE</f>
@@ -20660,8 +20330,7 @@
         <v>1</v>
       </c>
       <c r="G332" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H332" s="3" t="b">
         <f>FALSE</f>
@@ -20713,7 +20382,6 @@
         <v>23</v>
       </c>
       <c r="G333" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H333" s="3" t="b">
@@ -20766,7 +20434,6 @@
         <v>8</v>
       </c>
       <c r="G334" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H334" s="3" t="b">
@@ -20819,8 +20486,7 @@
         <v>20</v>
       </c>
       <c r="G335" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H335" s="3" t="b">
         <f>FALSE</f>
@@ -20872,7 +20538,6 @@
         <v>0</v>
       </c>
       <c r="G336" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H336" s="3" t="b">
@@ -20925,7 +20590,6 @@
         <v>3</v>
       </c>
       <c r="G337" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H337" s="3" t="b">
@@ -20978,7 +20642,6 @@
         <v>17</v>
       </c>
       <c r="G338" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H338" s="3" t="b">
@@ -21031,7 +20694,6 @@
         <v>0</v>
       </c>
       <c r="G339" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H339" s="3" t="b">
@@ -21084,8 +20746,7 @@
         <v>0</v>
       </c>
       <c r="G340" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H340" s="3" t="b">
         <f>FALSE</f>
@@ -21137,8 +20798,7 @@
         <v>0</v>
       </c>
       <c r="G341" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H341" s="3" t="b">
         <f>FALSE</f>
@@ -21190,8 +20850,7 @@
         <v>0</v>
       </c>
       <c r="G342" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H342" s="3" t="b">
         <f>FALSE</f>
@@ -21243,8 +20902,7 @@
         <v>0</v>
       </c>
       <c r="G343" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H343" s="3" t="b">
         <f>FALSE</f>
@@ -21296,8 +20954,7 @@
         <v>0</v>
       </c>
       <c r="G344" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H344" s="3" t="b">
         <f>FALSE</f>
@@ -21349,8 +21006,7 @@
         <v>0</v>
       </c>
       <c r="G345" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H345" s="3" t="b">
         <f>FALSE</f>
@@ -21402,8 +21058,7 @@
         <v>28</v>
       </c>
       <c r="G346" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H346" s="3" t="b">
         <f>FALSE</f>
@@ -21455,8 +21110,7 @@
         <v>0</v>
       </c>
       <c r="G347" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H347" s="3" t="b">
         <f>FALSE</f>
@@ -21508,8 +21162,7 @@
         <v>0</v>
       </c>
       <c r="G348" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H348" s="3" t="b">
         <f>FALSE</f>
@@ -21561,7 +21214,6 @@
         <v>0</v>
       </c>
       <c r="G349" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H349" s="3" t="b">
@@ -21614,7 +21266,6 @@
         <v>0</v>
       </c>
       <c r="G350" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H350" s="3" t="b">
@@ -21667,8 +21318,7 @@
         <v>0</v>
       </c>
       <c r="G351" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H351" s="3" t="b">
         <f>FALSE</f>
@@ -21720,8 +21370,7 @@
         <v>0</v>
       </c>
       <c r="G352" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H352" s="3" t="b">
         <f>FALSE</f>
@@ -21773,8 +21422,7 @@
         <v>4</v>
       </c>
       <c r="G353" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H353" s="3" t="b">
         <f>FALSE</f>
@@ -21826,7 +21474,6 @@
         <v>0</v>
       </c>
       <c r="G354" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H354" s="3" t="b">
@@ -21879,7 +21526,6 @@
         <v>0</v>
       </c>
       <c r="G355" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H355" s="3" t="b">
@@ -21932,7 +21578,6 @@
         <v>1</v>
       </c>
       <c r="G356" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H356" s="3" t="b">
@@ -21985,7 +21630,6 @@
         <v>2</v>
       </c>
       <c r="G357" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H357" s="3" t="b">
@@ -22038,7 +21682,6 @@
         <v>0</v>
       </c>
       <c r="G358" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H358" s="3" t="b">
@@ -22091,7 +21734,6 @@
         <v>8</v>
       </c>
       <c r="G359" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H359" s="3" t="b">
@@ -22144,7 +21786,6 @@
         <v>44</v>
       </c>
       <c r="G360" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H360" s="3" t="b">
@@ -22197,7 +21838,6 @@
         <v>60</v>
       </c>
       <c r="G361" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H361" s="3" t="b">
@@ -22250,7 +21890,6 @@
         <v>3</v>
       </c>
       <c r="G362" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H362" s="3" t="b">
@@ -22303,7 +21942,6 @@
         <v>17</v>
       </c>
       <c r="G363" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H363" s="3" t="b">
@@ -22356,8 +21994,7 @@
         <v>37</v>
       </c>
       <c r="G364" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H364" s="3" t="b">
         <f>FALSE</f>
@@ -22409,8 +22046,7 @@
         <v>0</v>
       </c>
       <c r="G365" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H365" s="3" t="b">
         <f>FALSE</f>
@@ -22462,8 +22098,7 @@
         <v>0</v>
       </c>
       <c r="G366" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H366" s="3" t="b">
         <f>FALSE</f>
@@ -22515,8 +22150,7 @@
         <v>0</v>
       </c>
       <c r="G367" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H367" s="3" t="b">
         <f>FALSE</f>
@@ -22568,8 +22202,7 @@
         <v>0</v>
       </c>
       <c r="G368" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H368" s="3" t="b">
         <f>FALSE</f>
@@ -22621,7 +22254,6 @@
         <v>1</v>
       </c>
       <c r="G369" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H369" s="3" t="b">
@@ -22674,8 +22306,7 @@
         <v>13</v>
       </c>
       <c r="G370" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H370" s="3" t="b">
         <f>FALSE</f>
@@ -22727,8 +22358,7 @@
         <v>1</v>
       </c>
       <c r="G371" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H371" s="3" t="b">
         <f>FALSE</f>
@@ -22780,8 +22410,7 @@
         <v>0</v>
       </c>
       <c r="G372" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H372" s="3" t="b">
         <f>FALSE</f>
@@ -22833,7 +22462,6 @@
         <v>9</v>
       </c>
       <c r="G373" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H373" s="3" t="b">
@@ -22886,8 +22514,7 @@
         <v>32</v>
       </c>
       <c r="G374" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H374" s="3" t="b">
         <f>FALSE</f>
@@ -22939,8 +22566,7 @@
         <v>0</v>
       </c>
       <c r="G375" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H375" s="3" t="b">
         <f>FALSE</f>
@@ -22992,7 +22618,6 @@
         <v>0</v>
       </c>
       <c r="G376" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H376" s="3" t="b">
@@ -23045,7 +22670,6 @@
         <v>0</v>
       </c>
       <c r="G377" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H377" s="3" t="b">
@@ -23098,7 +22722,6 @@
         <v>1</v>
       </c>
       <c r="G378" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H378" s="3" t="b">
@@ -23151,8 +22774,7 @@
         <v>19</v>
       </c>
       <c r="G379" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H379" s="3" t="b">
         <f>FALSE</f>
@@ -23204,7 +22826,6 @@
         <v>0</v>
       </c>
       <c r="G380" s="3" t="b">
-        <f>FALSE</f>
         <v>0</v>
       </c>
       <c r="H380" s="3" t="b">
@@ -23257,8 +22878,7 @@
         <v>0</v>
       </c>
       <c r="G381" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H381" s="3" t="b">
         <f>FALSE</f>
@@ -23310,8 +22930,7 @@
         <v>16</v>
       </c>
       <c r="G382" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H382" s="3" t="b">
         <f>FALSE</f>
@@ -23363,8 +22982,7 @@
         <v>0</v>
       </c>
       <c r="G383" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H383" s="3" t="b">
         <f>FALSE</f>
@@ -23416,7 +23034,6 @@
         <v>0</v>
       </c>
       <c r="G384" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H384" s="3" t="b">
@@ -23469,7 +23086,6 @@
         <v>11</v>
       </c>
       <c r="G385" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H385" s="3" t="b">
@@ -23522,7 +23138,6 @@
         <v>14</v>
       </c>
       <c r="G386" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H386" s="3" t="b">
@@ -23575,7 +23190,6 @@
         <v>19</v>
       </c>
       <c r="G387" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H387" s="3" t="b">
@@ -23628,8 +23242,7 @@
         <v>10</v>
       </c>
       <c r="G388" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H388" s="3" t="b">
         <f>FALSE</f>
@@ -23681,8 +23294,7 @@
         <v>0</v>
       </c>
       <c r="G389" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H389" s="3" t="b">
         <f>FALSE</f>
@@ -23734,8 +23346,7 @@
         <v>0</v>
       </c>
       <c r="G390" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H390" s="3" t="b">
         <f>FALSE</f>
@@ -23787,8 +23398,7 @@
         <v>4</v>
       </c>
       <c r="G391" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H391" s="3" t="b">
         <f>FALSE</f>
@@ -23840,8 +23450,7 @@
         <v>8</v>
       </c>
       <c r="G392" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H392" s="3" t="b">
         <f>FALSE</f>
@@ -23893,8 +23502,7 @@
         <v>2</v>
       </c>
       <c r="G393" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H393" s="3" t="b">
         <f>FALSE</f>
@@ -23946,8 +23554,7 @@
         <v>0</v>
       </c>
       <c r="G394" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H394" s="3" t="b">
         <f>FALSE</f>
@@ -23999,8 +23606,7 @@
         <v>0</v>
       </c>
       <c r="G395" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H395" s="3" t="b">
         <f>FALSE</f>
@@ -24052,8 +23658,7 @@
         <v>0</v>
       </c>
       <c r="G396" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H396" s="3" t="b">
         <f>FALSE</f>
@@ -24105,8 +23710,7 @@
         <v>0</v>
       </c>
       <c r="G397" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H397" s="3" t="b">
         <f>FALSE</f>
@@ -24158,8 +23762,7 @@
         <v>0</v>
       </c>
       <c r="G398" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H398" s="3" t="b">
         <f>FALSE</f>
@@ -24211,8 +23814,7 @@
         <v>0</v>
       </c>
       <c r="G399" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H399" s="3" t="b">
         <f>FALSE</f>
@@ -24264,7 +23866,6 @@
         <v>0</v>
       </c>
       <c r="G400" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H400" s="3" t="b">
@@ -24317,8 +23918,7 @@
         <v>0</v>
       </c>
       <c r="G401" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H401" s="3" t="b">
         <f>FALSE</f>
@@ -24370,8 +23970,7 @@
         <v>0</v>
       </c>
       <c r="G402" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H402" s="3" t="b">
         <f>FALSE</f>
@@ -24423,8 +24022,7 @@
         <v>0</v>
       </c>
       <c r="G403" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H403" s="3" t="b">
         <f>FALSE</f>
@@ -24476,8 +24074,7 @@
         <v>0</v>
       </c>
       <c r="G404" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H404" s="3" t="b">
         <f>FALSE</f>
@@ -24529,8 +24126,7 @@
         <v>0</v>
       </c>
       <c r="G405" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H405" s="3" t="b">
         <f>FALSE</f>
@@ -24582,8 +24178,7 @@
         <v>0</v>
       </c>
       <c r="G406" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H406" s="3" t="b">
         <f>FALSE</f>
@@ -24635,7 +24230,6 @@
         <v>0</v>
       </c>
       <c r="G407" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H407" s="3" t="b">
@@ -24688,8 +24282,7 @@
         <v>0</v>
       </c>
       <c r="G408" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H408" s="3" t="b">
         <f>FALSE</f>
@@ -24741,7 +24334,6 @@
         <v>34</v>
       </c>
       <c r="G409" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H409" s="3" t="b">
@@ -24794,7 +24386,6 @@
         <v>13</v>
       </c>
       <c r="G410" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H410" s="3" t="b">
@@ -24847,8 +24438,7 @@
         <v>7</v>
       </c>
       <c r="G411" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H411" s="3" t="b">
         <f>FALSE</f>
@@ -24900,7 +24490,6 @@
         <v>6</v>
       </c>
       <c r="G412" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H412" s="3" t="b">
@@ -24953,8 +24542,7 @@
         <v>4</v>
       </c>
       <c r="G413" s="3" t="b">
-        <f>TRUE</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H413" s="3" t="b">
         <f>FALSE</f>
@@ -25006,7 +24594,6 @@
         <v>3</v>
       </c>
       <c r="G414" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H414" s="3" t="b">
@@ -25059,7 +24646,6 @@
         <v>1</v>
       </c>
       <c r="G415" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H415" s="3" t="b">
@@ -25112,7 +24698,6 @@
         <v>5</v>
       </c>
       <c r="G416" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H416" s="3" t="b">
@@ -25165,7 +24750,6 @@
         <v>0</v>
       </c>
       <c r="G417" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H417" s="3" t="b">
@@ -25218,7 +24802,6 @@
         <v>19</v>
       </c>
       <c r="G418" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H418" s="3" t="b">
@@ -25271,8 +24854,7 @@
         <v>11</v>
       </c>
       <c r="G419" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H419" s="3" t="b">
         <f>FALSE</f>
@@ -25324,7 +24906,6 @@
         <v>2</v>
       </c>
       <c r="G420" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H420" s="3" t="b">
@@ -25377,7 +24958,6 @@
         <v>0</v>
       </c>
       <c r="G421" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H421" s="3" t="b">
@@ -25430,7 +25010,6 @@
         <v>0</v>
       </c>
       <c r="G422" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H422" s="3" t="b">
@@ -25483,7 +25062,6 @@
         <v>0</v>
       </c>
       <c r="G423" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H423" s="3" t="b">
@@ -25536,7 +25114,6 @@
         <v>0</v>
       </c>
       <c r="G424" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H424" s="3" t="b">
@@ -25589,7 +25166,6 @@
         <v>0</v>
       </c>
       <c r="G425" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H425" s="3" t="b">
@@ -25642,7 +25218,6 @@
         <v>0</v>
       </c>
       <c r="G426" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H426" s="3" t="b">
@@ -25695,7 +25270,6 @@
         <v>0</v>
       </c>
       <c r="G427" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H427" s="3" t="b">
@@ -25748,7 +25322,6 @@
         <v>0</v>
       </c>
       <c r="G428" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H428" s="3" t="b">
@@ -25801,7 +25374,6 @@
         <v>0</v>
       </c>
       <c r="G429" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H429" s="3" t="b">
@@ -25854,7 +25426,6 @@
         <v>0</v>
       </c>
       <c r="G430" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H430" s="3" t="b">
@@ -25907,7 +25478,6 @@
         <v>0</v>
       </c>
       <c r="G431" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H431" s="3" t="b">
@@ -25960,7 +25530,6 @@
         <v>0</v>
       </c>
       <c r="G432" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H432" s="3" t="b">
@@ -26013,7 +25582,6 @@
         <v>0</v>
       </c>
       <c r="G433" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H433" s="3" t="b">
@@ -26066,7 +25634,6 @@
         <v>0</v>
       </c>
       <c r="G434" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H434" s="3" t="b">
@@ -26119,7 +25686,6 @@
         <v>0</v>
       </c>
       <c r="G435" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H435" s="3" t="b">
@@ -26172,7 +25738,6 @@
         <v>0</v>
       </c>
       <c r="G436" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H436" s="3" t="b">
@@ -26225,7 +25790,6 @@
         <v>0</v>
       </c>
       <c r="G437" s="3" t="b">
-        <f>TRUE</f>
         <v>1</v>
       </c>
       <c r="H437" s="3" t="b">

--- a/backend/data/map_v4.6.xlsx
+++ b/backend/data/map_v4.6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fahmy\PycharmProjects\syncDashboard\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA77BB0C-C605-4655-A89D-F3AB36CD65F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16E2150-0BA4-44DF-BCD8-4CD464398461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58F0FD76-519D-46BD-9AA4-233998471043}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{58F0FD76-519D-46BD-9AA4-233998471043}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2753,7 +2753,26 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3084,26 +3103,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F7AB2-2F55-43AE-8970-69B0FC61725F}">
   <dimension ref="A1:O437"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.88671875" customWidth="1"/>
     <col min="13" max="13" width="37" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="37" customWidth="1"/>
-    <col min="15" max="15" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3150,7 +3169,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>762</v>
       </c>
@@ -3202,7 +3221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>762</v>
       </c>
@@ -3254,7 +3273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>762</v>
       </c>
@@ -3306,7 +3325,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>762</v>
       </c>
@@ -3358,7 +3377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>762</v>
       </c>
@@ -3410,7 +3429,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>762</v>
       </c>
@@ -3462,7 +3481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>762</v>
       </c>
@@ -3514,7 +3533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>762</v>
       </c>
@@ -3566,7 +3585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>762</v>
       </c>
@@ -3618,7 +3637,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>763</v>
       </c>
@@ -3670,7 +3689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>763</v>
       </c>
@@ -3722,7 +3741,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>763</v>
       </c>
@@ -3774,7 +3793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>763</v>
       </c>
@@ -3826,7 +3845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>763</v>
       </c>
@@ -3878,7 +3897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>764</v>
       </c>
@@ -3930,7 +3949,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>764</v>
       </c>
@@ -3982,7 +4001,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>764</v>
       </c>
@@ -4034,7 +4053,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>764</v>
       </c>
@@ -4086,7 +4105,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>765</v>
       </c>
@@ -4109,8 +4128,8 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I20" s="3" t="b">
         <f>TRUE</f>
@@ -4138,7 +4157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>765</v>
       </c>
@@ -4161,8 +4180,8 @@
         <v>1</v>
       </c>
       <c r="H21" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="b">
         <f>TRUE</f>
@@ -4190,7 +4209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>765</v>
       </c>
@@ -4242,7 +4261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>766</v>
       </c>
@@ -4294,7 +4313,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>766</v>
       </c>
@@ -4346,7 +4365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>766</v>
       </c>
@@ -4398,7 +4417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>766</v>
       </c>
@@ -4450,7 +4469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>766</v>
       </c>
@@ -4502,7 +4521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>767</v>
       </c>
@@ -4554,7 +4573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>767</v>
       </c>
@@ -4606,7 +4625,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>767</v>
       </c>
@@ -4658,7 +4677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>767</v>
       </c>
@@ -4710,7 +4729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>767</v>
       </c>
@@ -4762,7 +4781,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>767</v>
       </c>
@@ -4814,7 +4833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>767</v>
       </c>
@@ -4866,7 +4885,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>767</v>
       </c>
@@ -4918,7 +4937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>767</v>
       </c>
@@ -4970,7 +4989,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>767</v>
       </c>
@@ -5022,7 +5041,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>767</v>
       </c>
@@ -5074,7 +5093,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>767</v>
       </c>
@@ -5126,7 +5145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>767</v>
       </c>
@@ -5178,7 +5197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>767</v>
       </c>
@@ -5230,7 +5249,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>763</v>
       </c>
@@ -5282,7 +5301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>765</v>
       </c>
@@ -5334,7 +5353,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>765</v>
       </c>
@@ -5357,8 +5376,8 @@
         <v>1</v>
       </c>
       <c r="H44" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I44" s="3" t="b">
         <f>TRUE</f>
@@ -5386,7 +5405,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>765</v>
       </c>
@@ -5438,7 +5457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>765</v>
       </c>
@@ -5490,7 +5509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>766</v>
       </c>
@@ -5542,7 +5561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>766</v>
       </c>
@@ -5594,7 +5613,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>767</v>
       </c>
@@ -5646,7 +5665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>767</v>
       </c>
@@ -5698,7 +5717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>767</v>
       </c>
@@ -5750,7 +5769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>766</v>
       </c>
@@ -5802,7 +5821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>767</v>
       </c>
@@ -5854,7 +5873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>766</v>
       </c>
@@ -5906,7 +5925,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>766</v>
       </c>
@@ -5958,7 +5977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>762</v>
       </c>
@@ -6010,7 +6029,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>762</v>
       </c>
@@ -6062,7 +6081,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>762</v>
       </c>
@@ -6114,7 +6133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>762</v>
       </c>
@@ -6166,7 +6185,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>762</v>
       </c>
@@ -6218,7 +6237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>762</v>
       </c>
@@ -6270,7 +6289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>763</v>
       </c>
@@ -6322,7 +6341,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>763</v>
       </c>
@@ -6374,7 +6393,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>763</v>
       </c>
@@ -6426,7 +6445,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>763</v>
       </c>
@@ -6478,7 +6497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>763</v>
       </c>
@@ -6530,7 +6549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>765</v>
       </c>
@@ -6582,7 +6601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>766</v>
       </c>
@@ -6634,7 +6653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>766</v>
       </c>
@@ -6686,7 +6705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>767</v>
       </c>
@@ -6738,7 +6757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>767</v>
       </c>
@@ -6790,7 +6809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>767</v>
       </c>
@@ -6842,7 +6861,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>767</v>
       </c>
@@ -6894,7 +6913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>767</v>
       </c>
@@ -6946,7 +6965,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>767</v>
       </c>
@@ -6998,7 +7017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>767</v>
       </c>
@@ -7050,7 +7069,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>763</v>
       </c>
@@ -7102,7 +7121,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>763</v>
       </c>
@@ -7154,7 +7173,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>763</v>
       </c>
@@ -7206,7 +7225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>763</v>
       </c>
@@ -7258,7 +7277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>764</v>
       </c>
@@ -7310,7 +7329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>765</v>
       </c>
@@ -7333,8 +7352,8 @@
         <v>1</v>
       </c>
       <c r="H82" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I82" s="3" t="b">
         <f>TRUE</f>
@@ -7362,7 +7381,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>767</v>
       </c>
@@ -7414,7 +7433,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>767</v>
       </c>
@@ -7466,7 +7485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>767</v>
       </c>
@@ -7518,7 +7537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>762</v>
       </c>
@@ -7570,7 +7589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>762</v>
       </c>
@@ -7622,7 +7641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>762</v>
       </c>
@@ -7674,7 +7693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>762</v>
       </c>
@@ -7726,7 +7745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>762</v>
       </c>
@@ -7778,7 +7797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>762</v>
       </c>
@@ -7830,7 +7849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>762</v>
       </c>
@@ -7882,7 +7901,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>762</v>
       </c>
@@ -7934,7 +7953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>762</v>
       </c>
@@ -7986,7 +8005,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>762</v>
       </c>
@@ -8038,7 +8057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>763</v>
       </c>
@@ -8090,7 +8109,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>763</v>
       </c>
@@ -8142,7 +8161,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>763</v>
       </c>
@@ -8194,7 +8213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>763</v>
       </c>
@@ -8246,7 +8265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>763</v>
       </c>
@@ -8298,7 +8317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>763</v>
       </c>
@@ -8350,7 +8369,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>765</v>
       </c>
@@ -8402,7 +8421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>767</v>
       </c>
@@ -8454,7 +8473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>764</v>
       </c>
@@ -8506,7 +8525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>762</v>
       </c>
@@ -8558,7 +8577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>762</v>
       </c>
@@ -8610,7 +8629,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>762</v>
       </c>
@@ -8662,7 +8681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>762</v>
       </c>
@@ -8714,7 +8733,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>762</v>
       </c>
@@ -8766,7 +8785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>762</v>
       </c>
@@ -8818,7 +8837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>762</v>
       </c>
@@ -8870,7 +8889,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>763</v>
       </c>
@@ -8922,7 +8941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>763</v>
       </c>
@@ -8974,7 +8993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>763</v>
       </c>
@@ -9026,7 +9045,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>763</v>
       </c>
@@ -9078,7 +9097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>764</v>
       </c>
@@ -9130,7 +9149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>764</v>
       </c>
@@ -9182,7 +9201,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>765</v>
       </c>
@@ -9234,7 +9253,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>765</v>
       </c>
@@ -9286,7 +9305,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>767</v>
       </c>
@@ -9338,7 +9357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>767</v>
       </c>
@@ -9390,7 +9409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>767</v>
       </c>
@@ -9442,7 +9461,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>767</v>
       </c>
@@ -9494,7 +9513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>767</v>
       </c>
@@ -9546,7 +9565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>767</v>
       </c>
@@ -9598,7 +9617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>767</v>
       </c>
@@ -9650,7 +9669,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>767</v>
       </c>
@@ -9702,7 +9721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>767</v>
       </c>
@@ -9754,7 +9773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>767</v>
       </c>
@@ -9806,7 +9825,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>767</v>
       </c>
@@ -9858,7 +9877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>767</v>
       </c>
@@ -9910,7 +9929,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>767</v>
       </c>
@@ -9962,7 +9981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>763</v>
       </c>
@@ -10014,7 +10033,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>765</v>
       </c>
@@ -10066,7 +10085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>765</v>
       </c>
@@ -10089,8 +10108,8 @@
         <v>1</v>
       </c>
       <c r="H135" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I135" s="3" t="b">
         <f>TRUE</f>
@@ -10118,7 +10137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>765</v>
       </c>
@@ -10170,7 +10189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>767</v>
       </c>
@@ -10222,7 +10241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>767</v>
       </c>
@@ -10274,7 +10293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>762</v>
       </c>
@@ -10326,7 +10345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>762</v>
       </c>
@@ -10378,7 +10397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>763</v>
       </c>
@@ -10430,7 +10449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>763</v>
       </c>
@@ -10482,7 +10501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>763</v>
       </c>
@@ -10534,7 +10553,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>763</v>
       </c>
@@ -10586,7 +10605,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>767</v>
       </c>
@@ -10638,7 +10657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>767</v>
       </c>
@@ -10690,7 +10709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>767</v>
       </c>
@@ -10742,7 +10761,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>763</v>
       </c>
@@ -10794,7 +10813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>763</v>
       </c>
@@ -10846,7 +10865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>763</v>
       </c>
@@ -10898,7 +10917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>763</v>
       </c>
@@ -10950,7 +10969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>767</v>
       </c>
@@ -11002,7 +11021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>767</v>
       </c>
@@ -11054,7 +11073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>767</v>
       </c>
@@ -11106,7 +11125,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>762</v>
       </c>
@@ -11158,7 +11177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>762</v>
       </c>
@@ -11210,7 +11229,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>762</v>
       </c>
@@ -11262,7 +11281,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>762</v>
       </c>
@@ -11314,7 +11333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>762</v>
       </c>
@@ -11366,7 +11385,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>762</v>
       </c>
@@ -11418,7 +11437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>762</v>
       </c>
@@ -11470,7 +11489,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>762</v>
       </c>
@@ -11522,7 +11541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>762</v>
       </c>
@@ -11574,7 +11593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>767</v>
       </c>
@@ -11626,7 +11645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>764</v>
       </c>
@@ -11678,7 +11697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>763</v>
       </c>
@@ -11730,7 +11749,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>767</v>
       </c>
@@ -11782,7 +11801,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>766</v>
       </c>
@@ -11834,7 +11853,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>766</v>
       </c>
@@ -11886,7 +11905,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>765</v>
       </c>
@@ -11938,7 +11957,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>765</v>
       </c>
@@ -11990,7 +12009,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>765</v>
       </c>
@@ -12042,7 +12061,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>767</v>
       </c>
@@ -12094,7 +12113,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>767</v>
       </c>
@@ -12146,7 +12165,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>764</v>
       </c>
@@ -12198,7 +12217,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>766</v>
       </c>
@@ -12250,7 +12269,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>766</v>
       </c>
@@ -12302,7 +12321,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>767</v>
       </c>
@@ -12354,7 +12373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>763</v>
       </c>
@@ -12406,7 +12425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>762</v>
       </c>
@@ -12458,7 +12477,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>762</v>
       </c>
@@ -12510,7 +12529,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>762</v>
       </c>
@@ -12562,7 +12581,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>762</v>
       </c>
@@ -12614,7 +12633,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>763</v>
       </c>
@@ -12666,7 +12685,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>763</v>
       </c>
@@ -12718,7 +12737,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>763</v>
       </c>
@@ -12770,7 +12789,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>763</v>
       </c>
@@ -12822,7 +12841,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>764</v>
       </c>
@@ -12845,8 +12864,8 @@
         <v>1</v>
       </c>
       <c r="H188" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I188" s="3" t="b">
         <f>TRUE</f>
@@ -12874,7 +12893,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>764</v>
       </c>
@@ -12926,7 +12945,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>765</v>
       </c>
@@ -12978,7 +12997,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>765</v>
       </c>
@@ -13030,7 +13049,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>765</v>
       </c>
@@ -13053,8 +13072,8 @@
         <v>1</v>
       </c>
       <c r="H192" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I192" s="3" t="b">
         <f>TRUE</f>
@@ -13082,7 +13101,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>765</v>
       </c>
@@ -13105,8 +13124,8 @@
         <v>1</v>
       </c>
       <c r="H193" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I193" s="3" t="b">
         <f>TRUE</f>
@@ -13134,7 +13153,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>766</v>
       </c>
@@ -13186,7 +13205,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>767</v>
       </c>
@@ -13238,7 +13257,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>767</v>
       </c>
@@ -13290,7 +13309,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>767</v>
       </c>
@@ -13342,7 +13361,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>767</v>
       </c>
@@ -13394,7 +13413,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>763</v>
       </c>
@@ -13446,7 +13465,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>764</v>
       </c>
@@ -13498,7 +13517,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>764</v>
       </c>
@@ -13550,7 +13569,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>764</v>
       </c>
@@ -13602,7 +13621,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>765</v>
       </c>
@@ -13654,7 +13673,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>765</v>
       </c>
@@ -13706,7 +13725,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>765</v>
       </c>
@@ -13758,7 +13777,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>765</v>
       </c>
@@ -13810,7 +13829,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>765</v>
       </c>
@@ -13862,7 +13881,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>767</v>
       </c>
@@ -13914,7 +13933,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>767</v>
       </c>
@@ -13966,7 +13985,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>762</v>
       </c>
@@ -14018,7 +14037,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>762</v>
       </c>
@@ -14070,7 +14089,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>762</v>
       </c>
@@ -14122,7 +14141,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>762</v>
       </c>
@@ -14174,7 +14193,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>763</v>
       </c>
@@ -14226,7 +14245,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>763</v>
       </c>
@@ -14278,7 +14297,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>763</v>
       </c>
@@ -14330,7 +14349,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>763</v>
       </c>
@@ -14382,7 +14401,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>764</v>
       </c>
@@ -14405,8 +14424,8 @@
         <v>1</v>
       </c>
       <c r="H218" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I218" s="3" t="b">
         <f>TRUE</f>
@@ -14434,7 +14453,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>764</v>
       </c>
@@ -14486,7 +14505,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>765</v>
       </c>
@@ -14538,7 +14557,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>765</v>
       </c>
@@ -14590,7 +14609,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>765</v>
       </c>
@@ -14642,7 +14661,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>765</v>
       </c>
@@ -14665,8 +14684,8 @@
         <v>1</v>
       </c>
       <c r="H223" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I223" s="3" t="b">
         <f>TRUE</f>
@@ -14694,7 +14713,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>766</v>
       </c>
@@ -14746,7 +14765,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>767</v>
       </c>
@@ -14798,7 +14817,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>767</v>
       </c>
@@ -14850,7 +14869,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>767</v>
       </c>
@@ -14902,7 +14921,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>767</v>
       </c>
@@ -14954,7 +14973,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>763</v>
       </c>
@@ -15006,7 +15025,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>762</v>
       </c>
@@ -15058,7 +15077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>764</v>
       </c>
@@ -15110,7 +15129,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>764</v>
       </c>
@@ -15162,7 +15181,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>765</v>
       </c>
@@ -15214,7 +15233,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>765</v>
       </c>
@@ -15266,7 +15285,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>765</v>
       </c>
@@ -15318,7 +15337,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>765</v>
       </c>
@@ -15370,7 +15389,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>765</v>
       </c>
@@ -15422,7 +15441,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>767</v>
       </c>
@@ -15474,7 +15493,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>767</v>
       </c>
@@ -15526,7 +15545,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>762</v>
       </c>
@@ -15578,7 +15597,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>762</v>
       </c>
@@ -15630,7 +15649,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>763</v>
       </c>
@@ -15682,7 +15701,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>765</v>
       </c>
@@ -15734,7 +15753,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>765</v>
       </c>
@@ -15786,7 +15805,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>766</v>
       </c>
@@ -15838,7 +15857,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>766</v>
       </c>
@@ -15890,7 +15909,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>766</v>
       </c>
@@ -15942,7 +15961,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>766</v>
       </c>
@@ -15994,7 +16013,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>766</v>
       </c>
@@ -16017,8 +16036,8 @@
         <v>1</v>
       </c>
       <c r="H249" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I249" s="3" t="b">
         <f>TRUE</f>
@@ -16046,7 +16065,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>766</v>
       </c>
@@ -16098,7 +16117,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>766</v>
       </c>
@@ -16150,7 +16169,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>766</v>
       </c>
@@ -16202,7 +16221,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>767</v>
       </c>
@@ -16254,7 +16273,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>762</v>
       </c>
@@ -16306,7 +16325,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>762</v>
       </c>
@@ -16358,7 +16377,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>762</v>
       </c>
@@ -16410,7 +16429,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>762</v>
       </c>
@@ -16462,7 +16481,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>763</v>
       </c>
@@ -16514,7 +16533,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>763</v>
       </c>
@@ -16566,7 +16585,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>763</v>
       </c>
@@ -16618,7 +16637,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>763</v>
       </c>
@@ -16670,7 +16689,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>763</v>
       </c>
@@ -16722,7 +16741,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>763</v>
       </c>
@@ -16774,7 +16793,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>764</v>
       </c>
@@ -16826,7 +16845,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>764</v>
       </c>
@@ -16878,7 +16897,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>764</v>
       </c>
@@ -16930,7 +16949,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>764</v>
       </c>
@@ -16982,7 +17001,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>764</v>
       </c>
@@ -17034,7 +17053,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>764</v>
       </c>
@@ -17086,7 +17105,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>764</v>
       </c>
@@ -17138,7 +17157,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>765</v>
       </c>
@@ -17190,7 +17209,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>765</v>
       </c>
@@ -17242,7 +17261,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>765</v>
       </c>
@@ -17294,7 +17313,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>765</v>
       </c>
@@ -17346,7 +17365,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>765</v>
       </c>
@@ -17398,7 +17417,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>765</v>
       </c>
@@ -17450,7 +17469,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>765</v>
       </c>
@@ -17502,7 +17521,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>765</v>
       </c>
@@ -17554,7 +17573,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>765</v>
       </c>
@@ -17606,7 +17625,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>766</v>
       </c>
@@ -17629,8 +17648,8 @@
         <v>1</v>
       </c>
       <c r="H280" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I280" s="3" t="b">
         <f>TRUE</f>
@@ -17658,7 +17677,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>766</v>
       </c>
@@ -17710,7 +17729,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>766</v>
       </c>
@@ -17762,7 +17781,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>766</v>
       </c>
@@ -17814,7 +17833,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>766</v>
       </c>
@@ -17866,7 +17885,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>766</v>
       </c>
@@ -17918,7 +17937,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>766</v>
       </c>
@@ -17970,7 +17989,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>766</v>
       </c>
@@ -18022,7 +18041,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>766</v>
       </c>
@@ -18074,7 +18093,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>766</v>
       </c>
@@ -18126,7 +18145,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>766</v>
       </c>
@@ -18178,7 +18197,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>766</v>
       </c>
@@ -18230,7 +18249,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>766</v>
       </c>
@@ -18282,7 +18301,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>766</v>
       </c>
@@ -18305,8 +18324,8 @@
         <v>1</v>
       </c>
       <c r="H293" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I293" s="3" t="b">
         <f>TRUE</f>
@@ -18334,7 +18353,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>767</v>
       </c>
@@ -18386,7 +18405,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>767</v>
       </c>
@@ -18438,7 +18457,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>767</v>
       </c>
@@ -18490,7 +18509,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>767</v>
       </c>
@@ -18542,7 +18561,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>767</v>
       </c>
@@ -18594,7 +18613,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>767</v>
       </c>
@@ -18646,7 +18665,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>763</v>
       </c>
@@ -18698,7 +18717,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>763</v>
       </c>
@@ -18750,7 +18769,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>766</v>
       </c>
@@ -18802,7 +18821,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>763</v>
       </c>
@@ -18854,7 +18873,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>762</v>
       </c>
@@ -18906,7 +18925,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>762</v>
       </c>
@@ -18958,7 +18977,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>762</v>
       </c>
@@ -19010,7 +19029,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>762</v>
       </c>
@@ -19062,7 +19081,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>762</v>
       </c>
@@ -19114,7 +19133,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>762</v>
       </c>
@@ -19166,7 +19185,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>762</v>
       </c>
@@ -19218,7 +19237,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>763</v>
       </c>
@@ -19270,7 +19289,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>763</v>
       </c>
@@ -19322,7 +19341,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>765</v>
       </c>
@@ -19374,7 +19393,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>762</v>
       </c>
@@ -19426,7 +19445,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>762</v>
       </c>
@@ -19478,7 +19497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>762</v>
       </c>
@@ -19530,7 +19549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>762</v>
       </c>
@@ -19582,7 +19601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>762</v>
       </c>
@@ -19634,7 +19653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>767</v>
       </c>
@@ -19686,7 +19705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>767</v>
       </c>
@@ -19738,7 +19757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>763</v>
       </c>
@@ -19790,7 +19809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>762</v>
       </c>
@@ -19842,7 +19861,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>767</v>
       </c>
@@ -19894,7 +19913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>767</v>
       </c>
@@ -19946,7 +19965,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>767</v>
       </c>
@@ -19998,7 +20017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>767</v>
       </c>
@@ -20050,7 +20069,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>762</v>
       </c>
@@ -20102,7 +20121,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>763</v>
       </c>
@@ -20154,7 +20173,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>762</v>
       </c>
@@ -20206,7 +20225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>762</v>
       </c>
@@ -20258,7 +20277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>762</v>
       </c>
@@ -20310,7 +20329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>767</v>
       </c>
@@ -20362,7 +20381,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>763</v>
       </c>
@@ -20414,7 +20433,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>763</v>
       </c>
@@ -20466,7 +20485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>763</v>
       </c>
@@ -20518,7 +20537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>767</v>
       </c>
@@ -20570,7 +20589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>767</v>
       </c>
@@ -20622,7 +20641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>763</v>
       </c>
@@ -20674,7 +20693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>763</v>
       </c>
@@ -20726,7 +20745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>767</v>
       </c>
@@ -20778,7 +20797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>767</v>
       </c>
@@ -20830,7 +20849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>767</v>
       </c>
@@ -20882,7 +20901,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>767</v>
       </c>
@@ -20934,7 +20953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>767</v>
       </c>
@@ -20986,7 +21005,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>767</v>
       </c>
@@ -21038,7 +21057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>767</v>
       </c>
@@ -21090,7 +21109,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>767</v>
       </c>
@@ -21142,7 +21161,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>767</v>
       </c>
@@ -21194,7 +21213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>767</v>
       </c>
@@ -21246,7 +21265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>767</v>
       </c>
@@ -21298,7 +21317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>767</v>
       </c>
@@ -21350,7 +21369,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>767</v>
       </c>
@@ -21402,7 +21421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>767</v>
       </c>
@@ -21454,7 +21473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>767</v>
       </c>
@@ -21506,7 +21525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>767</v>
       </c>
@@ -21558,7 +21577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>767</v>
       </c>
@@ -21610,7 +21629,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>767</v>
       </c>
@@ -21662,7 +21681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>764</v>
       </c>
@@ -21714,7 +21733,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>765</v>
       </c>
@@ -21766,7 +21785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>765</v>
       </c>
@@ -21818,7 +21837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>765</v>
       </c>
@@ -21841,8 +21860,8 @@
         <v>1</v>
       </c>
       <c r="H361" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I361" s="3" t="b">
         <f>TRUE</f>
@@ -21870,7 +21889,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>764</v>
       </c>
@@ -21922,7 +21941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>766</v>
       </c>
@@ -21974,7 +21993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>766</v>
       </c>
@@ -22026,7 +22045,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>763</v>
       </c>
@@ -22078,7 +22097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>763</v>
       </c>
@@ -22130,7 +22149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>763</v>
       </c>
@@ -22182,7 +22201,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>763</v>
       </c>
@@ -22234,7 +22253,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>764</v>
       </c>
@@ -22286,7 +22305,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>764</v>
       </c>
@@ -22338,7 +22357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>764</v>
       </c>
@@ -22390,7 +22409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>764</v>
       </c>
@@ -22442,7 +22461,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>762</v>
       </c>
@@ -22494,7 +22513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>762</v>
       </c>
@@ -22546,7 +22565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>762</v>
       </c>
@@ -22598,7 +22617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>762</v>
       </c>
@@ -22650,7 +22669,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>762</v>
       </c>
@@ -22702,7 +22721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>762</v>
       </c>
@@ -22754,7 +22773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>762</v>
       </c>
@@ -22806,7 +22825,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>762</v>
       </c>
@@ -22858,7 +22877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>762</v>
       </c>
@@ -22910,7 +22929,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>762</v>
       </c>
@@ -22962,7 +22981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>762</v>
       </c>
@@ -23014,7 +23033,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>764</v>
       </c>
@@ -23066,7 +23085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>766</v>
       </c>
@@ -23118,7 +23137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>766</v>
       </c>
@@ -23170,7 +23189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>766</v>
       </c>
@@ -23222,7 +23241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>766</v>
       </c>
@@ -23274,7 +23293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>766</v>
       </c>
@@ -23326,7 +23345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>766</v>
       </c>
@@ -23378,7 +23397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>766</v>
       </c>
@@ -23430,7 +23449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>766</v>
       </c>
@@ -23482,7 +23501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>762</v>
       </c>
@@ -23534,7 +23553,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>762</v>
       </c>
@@ -23586,7 +23605,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>762</v>
       </c>
@@ -23638,7 +23657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>762</v>
       </c>
@@ -23690,7 +23709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>762</v>
       </c>
@@ -23742,7 +23761,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>762</v>
       </c>
@@ -23794,7 +23813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>762</v>
       </c>
@@ -23846,7 +23865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>762</v>
       </c>
@@ -23898,7 +23917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>762</v>
       </c>
@@ -23950,7 +23969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>762</v>
       </c>
@@ -24002,7 +24021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>762</v>
       </c>
@@ -24054,7 +24073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>762</v>
       </c>
@@ -24106,7 +24125,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>762</v>
       </c>
@@ -24158,7 +24177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>762</v>
       </c>
@@ -24210,7 +24229,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>762</v>
       </c>
@@ -24262,7 +24281,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>762</v>
       </c>
@@ -24314,7 +24333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>766</v>
       </c>
@@ -24366,7 +24385,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>766</v>
       </c>
@@ -24418,7 +24437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>766</v>
       </c>
@@ -24470,7 +24489,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>764</v>
       </c>
@@ -24522,7 +24541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>764</v>
       </c>
@@ -24574,7 +24593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>764</v>
       </c>
@@ -24626,7 +24645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>766</v>
       </c>
@@ -24649,8 +24668,8 @@
         <v>1</v>
       </c>
       <c r="H415" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I415" s="3" t="b">
         <f>TRUE</f>
@@ -24678,7 +24697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>766</v>
       </c>
@@ -24730,7 +24749,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>766</v>
       </c>
@@ -24753,8 +24772,8 @@
         <v>1</v>
       </c>
       <c r="H417" s="3" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="I417" s="3" t="b">
         <f>TRUE</f>
@@ -24782,7 +24801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>767</v>
       </c>
@@ -24834,7 +24853,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>763</v>
       </c>
@@ -24886,7 +24905,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>765</v>
       </c>
@@ -24938,7 +24957,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>767</v>
       </c>
@@ -24990,7 +25009,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>767</v>
       </c>
@@ -25042,7 +25061,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>767</v>
       </c>
@@ -25094,7 +25113,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>762</v>
       </c>
@@ -25146,7 +25165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>762</v>
       </c>
@@ -25198,7 +25217,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>762</v>
       </c>
@@ -25250,7 +25269,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>762</v>
       </c>
@@ -25302,7 +25321,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>763</v>
       </c>
@@ -25354,7 +25373,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>763</v>
       </c>
@@ -25406,7 +25425,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>764</v>
       </c>
@@ -25458,7 +25477,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>765</v>
       </c>
@@ -25510,7 +25529,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>765</v>
       </c>
@@ -25562,7 +25581,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>765</v>
       </c>
@@ -25614,7 +25633,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>766</v>
       </c>
@@ -25666,7 +25685,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>766</v>
       </c>
@@ -25718,7 +25737,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>767</v>
       </c>
@@ -25770,7 +25789,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>767</v>
       </c>
@@ -25824,6 +25843,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O437" xr:uid="{949F7AB2-2F55-43AE-8970-69B0FC61725F}"/>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri"&amp;11&amp;K5C2D91 This message/document has been classified as “Internal”&amp;1#_x000D_</oddHeader>
